--- a/data/import_ready/projects.xlsx
+++ b/data/import_ready/projects.xlsx
@@ -419,32 +419,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>title *</t>
+          <t>Название *</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description *</t>
+          <t>Описание *</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>author *</t>
+          <t>Автор *</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>telegram_contact</t>
+          <t>Телеграм</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>Тематики</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>Трек</t>
         </is>
       </c>
     </row>

--- a/data/import_ready/projects.xlsx
+++ b/data/import_ready/projects.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,9899 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Система визуального контроля качества «Прокопий»</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Задача на семестр — реализовать агента-брифатора предназначенного для автоматизации сбора и формализации требований к визуальному контролю качества. Он взаимодействует с технологами и инженерами по ка</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Студент_794</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>@user_300</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Нить</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1) формируем список сущностей для выявления из текста
+2) находим способ считать сущности из текста
+3) формируем json
+4) подключаемся по API к трекерам</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Студент_927</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>@user_599</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SATIT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1) Необходимо реализовать 3Д аватара, который будет озвучивать наши аудио потоки и общаться с пользователем
+2) Необходимо реализовать агента, который будет анализировать происходящее на компьютере пол</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Студент_614</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>@user_161</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Biogotchi</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- Разработать концепцию проекта и определить образ финального результата
+- Определить состав MVP-решения со сроком до конца первого семестра
+- Составить Roadmap-проекта 
+- Определить метрики на MVP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Студент_431</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>@user_600</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Мультиагентная система обработки данных о здоровье (MAS EHR)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Подготовка и согласование технических требований к системе оптического распознавания символов (OCR), предназначенной для интеграции с Visual Language Model (VLM) агентами.
+Разработка системы, обеспеч</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Студент_091</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>@user_343</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Text diffusion models for triple extraction from unstructured text</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1. Обзор существующих технологий и статей
+2. Поиск установленных в литературе бенчмарков
+3. Поднятие похожих решений если их нет на бенчмарке
+4. Написание MVP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Студент_055</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>@user_392</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Интеллектуальный 3D редактор облаков точек</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1, Провести эксперименты с различными моделями 3D детекции, сегментации
+2. Разработать базовые алгоритмы детекции динамических объектов на лидарных картах и единичных облаках точек
+3. Разработать прот</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Студент_122</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>@user_218</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Arabic llm</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/document/d/1XobcbPrWOodB3UOndVfhbwa2mkMhD9rNcSenvICxqwI/edit?usp=sharing
+накидали роудмап</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Студент_640</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>@user_184</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Метеомониторинг</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Реализация экспериментов по прогнозированию гололедообразования с помощью трансформера для временных рядов</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Студент_058</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>@user_043</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Deep fake recognition</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1. Ресерч по теме проекта: изучение литературы, существующих решений, текущего этапа работы и при наличии кодовой базы
+2. Участие в соревновании с командой проекта The Competition of Fairness in AI Fa</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Студент_114</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>@user_601</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AutoDS: Multi-Agent System for Automated Data Science</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1. Провести аналитический обзор научной литературы и существующих подходов к реализации AutoML на основе многоагентных систем (МАС) с использованием больших языковых моделей (БЯМ)
+2. Разработать базов</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Студент_108</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>@user_222</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Анализ и прогнозирование пользовательских отзывов с помощью базовых моделей машинного обучения (User Review Analysis and Prediction Using Basic Machine Learning Models)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проект выполняется в учебно-исследовательских целях: цель — изучить полный цикл решения ML-задачи (от загрузки данных до анализа результатов), закрепить понимание базовых алгоритмов (линейные модели, </t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Студент_060</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>@user_412</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Weather4cast</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Прошел отбор на проект в АИРИ лабораторию IMak, созвонились с командой. План: пробиваемся за счет мощной архитектуры на хакатоне по weather4cast, топ команд лидерборда будут публиковаться в журнале.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Студент_179</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>@user_142</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Генерация транзакций</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Проект по генерации банковских транзакций с использованием диффузионных моделей. На данный момент есть только TPP подходы, которые только категорию и время предсказывают на какой-то горизонт. Мы же ра</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Студент_111</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>@user_602</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TradingBench: Разработка бенчмарка работы LLM и агентских систем в финансовом и трейдинговом домене</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Провести research на тему - собрать литературу и сделать обзор.
+Собрать данные
+Спроектировать основу архитектуры</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Студент_109</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>@user_411</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Исследование применения функции оценки токенов для модели Transformer в контексте разреженности нейронных сетей</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Этап 1 
+ 1. Доработать текущий материал ВКР (а именно метод токенизации изображений с помощью функции оценки токенов)
+             1.1.       Организация репозитория с открытым и аккуратным исходным к</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Студент_075</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>@user_306</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Эмбеддеры низкой размерности  в Visual Place Recognition в условиях городской среды</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>План на семестр:
+Определить оптимальную низкоразмерную модель для определения геолокации в черте города. Изучить низкоразмерные VPR модели, сравнить их качество и скорость работы. Для этого:
+1. Опреде</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Студент_120</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>@user_603</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Научные исследования в NLP</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>- Обзор литературы и существующих подходов
+- Методология (цель, гипотезы, описание, метрики, датасет)
+- Эксперименты
+- Анализ результатов. Обсуждения
+- Заключение и список используемой литературы</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Студент_668</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>@user_200</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>МРТ</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1) Углубиться в теорию мрт
+2) Улучшить имеющиеся модели
+3) Предложить новое решение, которое улучшит метрики
+4) Найти подтверждающую литературу
+5) Написать набросок статьи о внедряемом решении</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Студент_408</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>@user_023</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Исследование задачи РЯЖ</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Еженедельные созвоны,  обсуждение задач, исследование темы и применение на практике</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Студент_698</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>@user_229</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ду́но (Адаптивные агенты, AIRI)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>мы договорились с научным руководителем что и я и он придумаем по 4 ресерч пропоузала и в течении 2 недель будем обсуждать дальнейшие планы и реализации</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Студент_450</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>@user_050</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Tokenisation methods adaptation for Russian language</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Продолжить работу над дипломной работой
+Проверит актуальность статей и информации на текущий момент 
+Выделить наиболее перспективные методы
+Построить или дополнить существующий пайплайн для обучени</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Студент_533</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>@user_604</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Marine Mammal Audio Respesentation Learning</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Провести исследование существующих архитектур, способных эффективно энкодить звуки животных, адаптировать их под звуки морских млекопитающих. Натренировать энкодер. Выбрать подходящие downstream задач</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Студент_005</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>@user_165</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Emotional TTS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Цель проекта - получить модель, которая синтезирует голос с заданной эмоцией. 
+1. Найти SOTA 2025 TTS модель
+2. Изучить подходящую модель (ее модули, пайплайн обучения\инференса и тд)
+3. Найти подход</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Студент_805</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>@user_221</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AI-метеоролог: многоагентная система для анализа погодных даных</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>На данный момент тематика LLM-агентов для задач описания физики погоды недостаточно хорошо раскрыта. Потенциал применения агентных систем в анализе метеорологических данных представлен в виде автомати</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Студент_059</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>@user_114</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ресерч токенизаторов ( названия нету, просто тема, которой занимался зашла Валентину ))</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Изучить актуальные исследования и материалы по токенизации для языковых моделей, чтобы сформировать целостное понимание современного состояния области и выявить ключевые направления развития.
+Проанал</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Студент_1253</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>@user_304</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>behavioral_twin_llm_fusion</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Обзор литературы и существующих решений:
+Изучение работ по implicit персонализации LLM (User-LLM, PPlug, E2P, ILM, UQABench и др.)
+Сравнение архитектурных подходов (soft prompt, cross-attention, Q-F</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Студент_100</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>@user_064</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>статья по теме "Leverage the inherent geometric and semantic priors from an existing multi-task model to enable self-supervised monocular depth completion."</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1. латексный драфт статьи - возможно не со всеми экспериментами, но понятна структура:
+* накидать всю структуру по исследовнию - все части 
+* с какими моделями будем сравнивать - на каких данных
+* мож</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Студент_121</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>@user_125</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Исследование моделей для векторного представления медицинских текстов</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>План работы:
+1. Изучение литературы по работе с мед. текстами 
+2. Поиск/формирование датасета для обучения и тестирования 
+3. Обзор моделей-конкурентов и подсчет выбранных метрик  на тестовом датас</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Студент_092</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>@user_003</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Copilot для Linux: инженерная разработка системы поддержки пользователей и приложений</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>На согласовании у руководителя практики. Согласование ожидается 13.10.2025 в течение дня</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Студент_068</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>@user_375</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Explainability и механическая интерпретируемость для защиты LLM</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Цель:
+Создать и протестировать low-latency гардрейл для LLM на основе sparse autoencoder (SAE), выделяющий вредоносные направления в активациях модели и блокирующий нежелательные ответы.
+Основные зад</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Студент_033</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>@user_295</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>AI Security Lab</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Проведу исследование защиты llm систем</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Студент_827</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>@user_318</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Исследование новостных нарративов</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Постановка задачи и анализ данных — уточнение целей исследования, выбор релевантных источников публикаций и экономических индикаторов, сбор, структурирование и предварительная очистка данных.
+Идентиф</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Студент_633</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>@user_605</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Диффузионные модели в NLP</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Изучил текущее состояние диффузии в тексте. Точная тема ресерча на уточнении</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Студент_650</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>@user_606</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Video Enhancement and Compression</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>- Обзор литературы
+- Baseline моделей
+- Тестирование гипотез
+- Подготовка данных</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Студент_123</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>@user_607</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Динамический трекинг клеток</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Сперва написать алгоритм потоковой обработки видео, подготовить данные. Провести сегментацию клеток и пытаться обучать физически ориентированную модель для возможности прогнозирования движения клетки</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Студент_093</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>@user_608</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Ancient languages and AI in Archeology</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1) Формирование итогового датасета и предобработка TLA (это корпус древнеегиптеских текстов и их переводы, разметка от египтологов) 
+2) Эксперименты с обучением эмбеддингов
+3) Качественная оценка эмбе</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Студент_027</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>@user_273</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Студент_115</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>@user_367</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Исследование экономических нарративов</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1.1 Очистить и структурировать данные из Telegram и других источников (новостные БД, соцсети).
+1.2 Применить фильтры по экономическим ключевым словам (как указано в презентации).
+1.3 Удалить шум и нер</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Студент_993</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>@user_447</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Multi-agent Reinforcement Learning for game theory and economics applications</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Изучение статей и литературы по направлению Multi-agent Reinforcement Learning
+Тестирование гипотез, проведение экспериментов и сбор данных с дальнейшим написанием статьи 
+(Цель "написание статьи" вхо</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Студент_669</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>@user_201</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>iMak AI Lab (10. Predictive maintenance)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Взять данные из соревнования на Kaggle 
+- Воспроизвести эксперимент на основе доступного в сети исследования
+- Зафиксировать результат эксперимента
+- Сравнить результат с решением исследовательской </t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Студент_057</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>@user_420</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Efficient Prompt Mechanistic Interpretability</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Пока что не собирались с куратором и не обсуждали, уже написал ему о необходимости составления плана</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Студент_924</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>@user_395</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Оцифровка тибетских документов института монголоведения буддологии и тибетологии СО РАН</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1. Подготовительный этап (1–2 неделя)
+Задачи:
+Согласование состава материалов, подлежащих оцифровке (рукописи, ксилографы, машинописные тексты).
+Определение технических требований к сканированию (р</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Студент_029</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>@user_260</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Научная статья связанная с RAG</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Отлично, у тебя уже есть направление — RAG (Retrieval-Augmented Generation) и конкретный фокус — верификация (проверка достоверности/релевантности) в контексте RAG. Ниже я предложу структуру плана дей</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Студент_046</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>@user_180</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Группа "ИИ в промышленности" Института искусственного интеллекта AIRI</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>План работы - построение агентской системы, включение uncertainty метрик, проведение экспериментов, замер метрик и определение финального пайплайна</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Студент_070</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>@user_609</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>LLM Agents Uncertainty</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- изучить релевантные статьи по LLM Uncertainty и LLM Agents Uncertainty
+- сформулировать теоретическую модель оценки неуверенности LLM агентов
+- предложить гипотезы для экспериментов
+- реализовать и </t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Студент_069</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>@user_610</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Deepfake detection</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>До конца октября командной соревнование по теме. При удачном раскладе - статья в научном журнале
+При очень хорошем раскладе - статья на конференции А*</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Студент_875</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>@user_352</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Исследование нарративов</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1. Изучить тему новостных нарративов
+2. Поработать с базой новостей телеграмм каналов
+3. Разработать модель для выявления нарративов на основе анализа текстов новостей и их распространения</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Студент_372</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>@user_004</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>LLM Agents Uncertainty</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>проверить ряд гипотез, основываясь на внутреннем представлении модели</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Студент_071</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>@user_376</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Graph Neural Networks for  Combinatorial Optimization</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>● Formulate any interesting Combinatorial Optimization problems as Quadratic Unconstrained Binary Optimization (QUBO) problem.
+● Design and train baseline unsupervised GNN models to optimize 
+QUBO obj</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Студент_401</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>@user_020</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Структурно-информированный генеративный дизайн белок-связывающих аптамеров посредством алгоритмов на основе обучения с подкреплением</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1. Знакомство с научной литературой и документацией по проекту
+2. Анализ существующих БД аптамер-таргет
+3. Поиск дескрипторов для нуклеотидных и аминокислотных последовательностей
+4. Разработка класси</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Студент_113</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>@user_053</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Исследование новостных нарративов</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1) "Вхождение в тему вопроса" исследование источников по нарративам
+2) Создание системы для сбора информации/датасета для анализа
+3) Построение модели предсказания валидности новости(mvp)
+4) тестирова</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Студент_689</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>@user_611</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Исследование подходов к генерации кода при помощи информационного поиска</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Описать план работы (подходы, эксперименты + сроки)
+Выбрать существующий benchmark и OpenSource llm.
+Провести эксперименты, показывающие, что добавление информационного поиска улучшает точность генера</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Студент_044</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>@user_612</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Студент_106</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>@user_613</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Научные исследования в NLP</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Пока идет подготовительная работа, поэтому точного плана нет.
+Основные шаги - это анализ научной области, подготовка экспериментов, в зависимости от их успешности либо дальнейшие эксперименты, либо пу</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Студент_048</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>@user_424</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Решение cross-lingual jailbreaking с помощью семантического анализа</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Анализ уязвимости cross-lingual jailbreaking: взять бенчмарки на англ популярные с вредоносными промптами и перевести их на несколько видов языков (октябрь)
+    2. Решение для нашей проблемы - это </t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Студент_035</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>@user_013</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Исследование нарративов</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Научиться выявлять нарративы на этапе публикации
+Научиться предсказывать период распространения (и первые 2-3 точки)
+Отследить распространение нарративов
+Научиться предсказывать влияние нарративов на </t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Студент_630</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>@user_175</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Raft Lab Research</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Большие языковые модели (LLM) – это мощный инструмент, но, как и любой инструмент, они могут быть использованы неправильно. Если мы не будем контролировать то, что они говорят, они могут распространя</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Студент_634</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>@user_178</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Анализ и выявление семантических дублей в новостях внешней торговли</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Я планирую последовательно уточнить критерии того, что считаем семантическим дублем новости (чтобы отличать перефраз одного и того же события от смежных сюжетов), собрать и очистить корпус новостей и </t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Студент_420</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>@user_030</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Разработка бенчмарка для мультиагентной системы экзаменатора</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1. Анализ существующей литературы по предметной области.
+2. Поиск подходящих бенчмарков и метрик для каждой компоненты мультиагентной системы.
+3. Сборка своего бенчмарка, на основе существующих датасе</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Студент_105</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>@user_614</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Исследование нарративов</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Исследование нарративов и возможных метрик для моделей</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Студент_448</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>@user_048</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>RAG verification</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Сначала обзор литературы
+Остальное не успели обсудить</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Студент_719</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>@user_245</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Оцифровку и перевод тибетских рукописей</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>- Реализация модели генерации синтетических данных для OCR тибетских рукописей
+- Анализ полученных результатов с помощью OCR системы, обученной на генерируемых данных</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Студент_418</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>@user_027</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Исследование новостных нарративов</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Основная цель нашей работы в этом семестре — составить прогноз российской экономики на основе данных о валюте, нефти и курсах акций, полученных из различных наборов данных. Для этого я сосредоточусь н</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Студент_536</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>@user_615</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Оцифровка и перевод тибетских рукописей</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>- Поиск, сбор и разметка исходных изображений тибетских рукописей и ксилографов
+- Исследование и реализация методов привязки текстовых и визуальных данных для создания мульти-модального датасета
+- Реа</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Студент_678</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>@user_206</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Бенчмарк для оценки влияния эмоций на поведение LLM моделей в контексте сложных экономических и социальных задач</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1) Обзор литературы
+2) Проектирование и таксономия новых теоретико-игровых сценариев
+3) Сбор, синтетическая генерация и разметка датасетов под разные эмоциональные условия
+4) Проверка валидности сцена</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Студент_481</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>@user_073</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Bio-inspired Multi-Agent RL MARL</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Первичный  анализ готовых экспериментальных данных
+Обзор литературы
+Поиск подходящей модели для описания экспериментальных данных</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Студент_088</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>@user_402</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>iMak AI Lab</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Работа над агентом для научных исследований:
+- анализ научной литературы
+- адаптация фреймворка holosophos для наших исследований
+- улучшение основного агента для написания статей</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Студент_104</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>@user_214</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AI Singularity (преакселератор), но я так понял это разные вещи: акселератор и стартап-трек</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Так как мы начали делать стартап с началом преакселератора, то ставлю целью на семестр -- готовый лендинг, не менее 50 глубинных интервью с целевой аудиторией, готовый дизайн / макеты iOS приложения и</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Студент_334</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>@user_302</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Древние языки и ИИ в археологии</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Погружение в контекст задачи: чтение научных статей, анализ датасетов и оценка существующих решений.
+Тестирование существующих ллм в зеро-шот режиме
+Дообучение различных ллм (включая Gemma-T5) на за</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Студент_936</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>@user_405</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Научные исследования в NLP</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1. План работы на семестр
+1.1 Определить требования к бенчмарку с учетом необходимости анализа репозиториев с кодом.
+1.2 Провести SAST-анализ репозиториев для получения списка потенциальных уязвимосте</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Студент_012</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>@user_322</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Efficient Prompting</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>План - проверить ряд гипотез, основываясь на внутреннем представлении модели. В результате создать бейзлайн-метрики для оценки промптов</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Студент_709</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>@user_239</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Explainability и механическая интерпретируемость для защиты LLM</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Исследование темы "Mechanistic steering и детекция".
+Измеряем проекции на подпространства “refusal/compliance”, изучаем компромиссы полезности и устойчивости к универсальным суффиксам.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Студент_654</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>@user_191</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Агентская система в образовании</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Написание статьи на https://aaai.org/conference/aaai/aaai-26/workshop-program-list/#ws14 или 
+https://2026.eacl.org/calls/demos/
+https://humanrobotinteraction.org/2026/videos-and-demos/
+https://percom</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Студент_022</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>@user_453</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Исследование новостных нарративов</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1. Анализ задачи и данных — определение целей исследования, отбор источников публикаций и экономических показателей, подготовка и очистка данных.
+2. Выявление нарративов — применение методов NLP и те</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Студент_370</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>@user_001</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Бенчмарк для оценки влияния эмоциональных состояний на поведение LLM в сложных экономических и социальных задачах</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1) Обзор литературы
+2) Проектирование и таксономия новых теоретико-игровых сценариев
+3) Сбор, синтетическая генерация и разметка датасетов под разные эмоциональные условия
+4) Проверка валидности сцена</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Студент_505</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>@user_092</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Исследование применения flow matching подхода к контролируемой генерации табличных данных</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1. Изучить дифузионные модели
+1.1 На канале Студент_2252 посмотреть лекции про сэмплирование
+1.2 Понять что такое генеративная модель (научиться сэмплировать данные)
+1.3 Изучить диффузионные модели (с</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Студент_1364</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>@user_616</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Deepfake generation and detection based on micro emotions Technology</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Загрузка тестового батча видео (тест скрипта загрузки с Ютуба)
+Адаптация загрузки видео для других платформ 
+Код для извлечения мета-признаков видео (FAUs, пол, возраст, раса, эмоции ...)
+Замена бэкгр</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Студент_064</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>@user_282</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Исследование нейросетей для распознания языка жестов</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Планируется провести сравнительный анализ подходов для распознания языка жестов и преобразования его в текст, а также обучение своего пайплайна для улучшения существующих метрик.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Студент_374</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>@user_006</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Научные исследования в NLP</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Планирую изучить литературу и нужно получить базовые знания в NLP
++ нужно обсудить план с научником</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Студент_082</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>@user_444</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ai в археологии (создание адаптированного к буддийским рукописям и ксилогрофам llm-based переводчика с тибетского языка)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1. Изучение редевантной литературы
+2. Написание кода
+3. Оценка получившегося переводчика
+…</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Студент_769</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>@user_279</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Определение размерности манифолда данных</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1. Читаю статьи по теме
+2. Пробую на разных датасетах/моделях смоделировать размерность 
+3. Идеально придти к какой-то идеи, но пока без конкретики</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Студент_053</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>@user_291</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Benchmark</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1. Изучить бенчмарки, сущетсвующие в AI Security.
+2. Выделить достоинства и недостатки сущетсвующих решений.
+3. Оценить, насколько текуищие бенчмарки обобщаются на мультиагентные системы.
+4. Изучить с</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Студент_677</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>@user_205</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>TRM Dual Norms</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+результат - реализованное изменение модели TRM из статьи (https://www.arxiv.org/pdf/2510.04871)  и замеры, сравнение с бейзлайном на ARC-AGI</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Студент_081</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>@user_617</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Deep fake detection</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Сота-метод (DreamID) - найти код, сделать энвир и протестить на загруженных видео
+Имплементация других методов на открытых датасетах</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Студент_063</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>@user_298</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>iMak AI Lab (Animals communication)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Погрузиться в тему обработки звука:
+Провести литобзор, проанализировать датасеты, архитектуру трансформеров, требования к данным 
+Выбрать вид животного (или нескольких) для изучения 
+Найти подходящий</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Студент_004</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>@user_434</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Бенчмаркинг мультиагентных систем</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Обзор источников по теме
+Построение гипотез
+Проверка гипотез, эксперименты
+Оценка результатов
+Работа над статьёй или публикация бенчмарка</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Студент_382</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>@user_014</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>iMak AI Lab</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1. Проанализировать современные варианты разработки эмбеддера звуков животных
+2. Собрать данные для обучения
+3. Обучить первую трансформерную модель
+4. Проэкспериментировать на различных задачах anima</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Студент_003</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>@user_427</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Поколенчески адаптированная генерация маркетинговых описаний с использованием больших языковых моделей: влияние языкового кода на воспринимаемую релевантность и конверсию</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Написание научной статьи</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Студент_061</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>@user_618</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AI4Science</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>исследование и доработка существующих решений agents4science. Разработка своего собственного.</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Студент_988</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>@user_619</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AI4Scoence</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">исследование и доработка существующих решений agents4science. Разработка своего собственного.
+</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Студент_908</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>@user_380</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AI agents for Science</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>исследование и доработка существующих решений agents4science. Разработка своего собственного.</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Студент_371</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>@user_002</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>МРТ от Genotek</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Воспроизвести бейзлайны UNet и VarNet, улучшить их</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Студент_1387</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>@user_620</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Применение больших языковых моделей для анализа безопасности кода</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Этап 1: Литературный обзор и анализ предметной области (4-6 недель)
+Недели 1-2: Систематический обзор современных LLM-подходов к анализу безопасности кода
+Недели 3-4: Анализ существующих датасетов и м</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Студент_037</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>@user_436</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Проекты от X5</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Я принят в один из проектов от X5 - Customer Choice Models, планирую выполнять задачи своего руководителя, цели и задачи чем буду заниматься уже были предоставлены.  Для меня это новый опыт, поэтому.
+</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Студент_954</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>@user_621</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>req assist</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Выкатить на дев и начать тестирование в рамках своей команды мое решение. Собрать ОС и улучшить продукт после ОС от аналитиков</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Студент_162</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>@user_059</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Речевые технологии Х5</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Основной задачей на этот семестр будет разработка метода оценки работы диаризации в текущем продукте и исследование для улучшиения диаризации. Для этого нужно
+- Собрать датасет для сбора метрик качест</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Студент_273</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>@user_241</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Static Avatars</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача - 3д реконструкция статичного человека. Съемка максимум 15 секунд
+Цель - максимизировать качество
+План
+1) выяснить насколько влияют микро движения человека на финальный результат 
+2) придумать </t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Студент_282</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>@user_323</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Система машинного перевода для низкоресурсных языков - TatSoft</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1) сбор и хранение параллельных корпусов пар языков (русский-татарский);
+2) систематизация и анализ НД;
+3) проведение аналитического обзора методов, технологий и инструментов в области МП текстов, выб</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Студент_1395</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>@user_622</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Интеллектуальный помощник для анализа корпоративных событий эмитентов ценных бумаг</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1) Изучить структуру и формат публикаций корпоративных сообщений на сайте e-disclosure.ru
+2)  Разработать парсер для автоматической выгрузки всех корпоративных новостей по дню 
+3) Разработать парсер</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Студент_238</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>@user_067</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Метеомониторинг</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>разработка модели классификации типов льда, улучшение модели регрессии веса обледенения, доработка инференса моделей классификации и регрессии</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Студент_190</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>@user_623</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Text-to-SQL система для сегментации пользователей</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Сбор чётких требований по качеству/производительности системы от заказчика
+2. Определение формата входных данных и ожидаемого ответа
+2. Анализ SOTA решений Text-to-SQL задач, основанных на агентах
+</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Студент_350</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>@user_079</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Genome AI</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1. Выровняться по текущей концепции (посмотреть расхождения с реальными процессами работы с геномом и тем что описано в документации и при необходимости внести корректировки) так как до этого была дру</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Студент_939</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>@user_408</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Генератор схем решения математических задач</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>- собрать оценочный пул математических задач с полным покрытием по школьной программе за 5-11 класс
+- размножить пул задач для генерации синтетического датасета с равномерным покрытием задач по всем т</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Студент_762</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>@user_276</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Студент_2253</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1. Разработка функционала QA с помощью RAG/Графах
+2. Разработка агента планирования отпусков
+3. Разработка ассистента документооборота (исправление типовых ошибок)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Студент_1409</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>@user_314</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Разработка программно-аппаратного комплекса для автоматического обнаружения, идентификации и полёта к заданному объекту на борту БВС</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1. Сбор требований, проектирование архитектуры решения, используемый подход для обеспечения необходимой эффективности, точности, скорости. А также ведение проекта внутри компании;
+2. Подготовка датасе</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Студент_303</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>@user_140</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>НАЁМ</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Видение и рамки: проблема, цели/non-goals, ограничения, стейкхолдеры, RACI, критерии успеха.
+2. Рынок и сегментация: ICP, JTBD-портреты, сегменты (лестница Ханта/отрасль/размер/гео), TAM/SAM/SOM, </t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Студент_526</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>@user_624</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>НАЁМ</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>6. Бизнес-процессы и сервис-дизайн: AS-IS/TO-BE, CJM рекрутера/кандидата, Service Blueprint точек внедрения.
+7. Use Cases / User Stories: инвентарь сценариев, ключевые UC, US с критериями приёмки (Gh</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Студент_1426</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>@user_454</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Узнай город</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Собрать данные для обучения модели детекции зданий
+2. Доообучить модель на этих данных
+3. Получить метрики качества модели
+4. Итеративно повышать качество предсказаний
+5. Интегрировать наработки в </t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Студент_874</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>@user_351</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>рабочий проект</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">общая идея - Self-Service аналитика на основе ИИ: любой сотрудник, от операционного менеджера до топ-руководителя, самостоятельно получает бизнес-инсайты и рекомендации по данным, без аналитиков, SQL </t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Студент_1432</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>@user_071</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>AI-агент по профориентации</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Полная реализация AI-агента по профориентиации от GIGASCHOOL</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Студент_739</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>@user_262</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Edu AI Hub</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Продолжить разработку и улучшение функционала платформы.</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Студент_321</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>@user_136</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Ранжирование каталога в мобильном приложении доставки еды</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Этап 1: Анализ данных и требований (Неделя 1-2)
+Этап 2: Проектирование системы (Неделя 3-4)
+Этап 3: Разработка модели (Неделя 5-8)
+Этап 4: Инфраструктура и развертывание (Неделя 9-10)
+Этап 5: Документ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Студент_514</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>@user_625</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>НАËМ</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>План семестра заключается в участии в утверждении архитектуры системы и проработке взаимодействия ML-сервисов, включая API Gateway, очереди сообщений и Data Lake, с возможным пересмотром решений по ит</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Студент_510</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>@user_469</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Заказчик - стартап travel-agency, работающее на рынке Катара. Им нужен сервис, который позволит автоматизировать либо существенно упростить подготовку коммерческих предложений для клиентов по полученн</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Студент_319</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>@user_090</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>OZON-банк call-центр</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Если используется 2‑канальная телефония (агент и клиент в отдельных каналах), диаризация не нужна. Мы разделяем и нормализуем каналы (16 кГц PCM, выравнивание уровня, лёгкий denoise), делаем VAD по ка</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Студент_921</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>@user_626</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Ai review | Я Практикум</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Разработать и протестировать подход к автоматическому анализу и валидации отзывов модели по коду, работающему с проектами в формате ZIP-архивов.
+Исследовать, как можно автоматически проверять коррект</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Студент_1449</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>@user_627</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Gigaschool</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Все будет оговорено на созвоне в выходные. Делаем проект для профориентации школьников.</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Студент_170</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>@user_226</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AI Media Producer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Задача: агент для генерации изображений на локальных open-source или недорогих SDXL-style моделях.
+В задачи разработки агента генерации изображений входят следующие этапы:
+- Изучение существующих реш</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Студент_377</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>@user_010</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Агенты в автоматизации поддержки</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>- Аналитика текущих процессов в отдельно взятых интентах поддержки
+- Коммуникация с аналитикой и бекендом
+- Создание прототипов на основе LLM
+- Исследовательский/АБ-тест
+- Поведение результатов
+- Обуч</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Студент_329</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>@user_363</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>LLM Agents в поддержке T-Tech</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Проект: LLM-агенты в поддержке T-Tech.
+Собрать и анонимизировать логи; разметить траектории с помощью crowdsource.
+Развернуть пайплайн: хранение, трейсинг, автотесты; симулятор тулов.
+Собрать агент</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Студент_307</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>@user_406</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Разработка компонента рекомендательной системы для сервиса подбора персонала</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1) Анализ данных
+2) Проектирование системы
+3) Построение пайплайна 
+4) Дообучение модели ранжирования
+5) Замер метрик</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Студент_309</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>@user_452</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Телеграм-бот с llm-агентом для поддержки клиентов интернет провайдера</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1. Составить техническое задание вместе с руководителем и менеджерами, которые общаются с клиентами.
+2. Создать llm-агента c инструментами:
+    2.1. Создать llm-систему авторизации клиентов в системе</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Студент_1005</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>@user_628</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Сервис интеллектуального поиска по строительной документации для  ООО «Студент_2256»</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1) Провести аудит текущих базы документов, имеющихся у компании ДжиминиСофт
+2) Провести детальную проработку арихтектуры решение и составление подробного ТЗ
+3) Провести эксперименты и разработать прот</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Студент_708</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>@user_238</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Улучшение системы бенчмаркинга</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Я работаю в R&amp;D команде ВКонтакте в разработке LLM.
+На текущий момент есть следующие точки роста в нашей системе бенчмаркинга:
+1. Использование GPT-as-judge
+Это приносит хорошие результаты, но тратит</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Студент_274</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>@user_127</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Поиск по артефактам компании с интеграций RAG</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основное:
+1.Улучшение рекомендательной системы
+Использование персонализированных данных пользователей для повышения релевантности рекомендаций и улучшения пользовательского опыта. Планируется анализ </t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Студент_249</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>@user_085</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ИИ-ассистент для LMS (CДО) Moodle</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Этапы внедрения:
+1. Пилотное тестирование на курсах гибких навыков и иностранных языков
+2. Адаптация под требования дополнительного образования
+3. Интеграция в общеуниверситетскую систему Moodle
+4. Ра</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Студент_512</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>@user_099</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Разработка сервиса по транскрибации и суммаризации звонков в службу поддержки</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Проанализировать область работы, доступные open-source модели для работы с аудио форматом, развернуть модель по транскрибации и диаризации на рабочих серверах, дообучить под корпоративные данные, напи</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Студент_1473</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>@user_629</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>AI-ассистент для аварийного обслуживания оборудования</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1. Исследование пользователей и процессов
+Проведение интервью с операторами, мастерами и инженерами
+Картирование текущего процесса устранения аварий
+Выявление ключевых проблем и ожиданий от ассистента</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Студент_508</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>@user_630</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Нить</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Пока что не было встречи с руководителем данного проекта</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Студент_761</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>@user_275</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>AI агент для поиска поиска информации в регуляторных документах ЦБ</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Разработка модели поиска информации в документации ЦБ
+Разработка модели генерации ответа, основываясь на найденной информации
+Тестирование системы на тестовых вопросах, которых не было в обучающей выб</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Студент_182</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>@user_487</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Речевые технологии Х5</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Разработать универсального агента для генерации суммаризаций для встреч &gt; 4 часов по заданным шаблонам</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Студент_1480</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>@user_404</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Матчинг адресов (ГПБ)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>- Изучение теоретических аспектов нормализации, разбора адресов на компоненты и алгоритмов информационного поиска/матчинга
+- Проектирование пайплайна обработки адресов
+- Выбор метрик для оценки качест</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Студент_150</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>@user_631</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Графовый анализ диалогов</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 шаг - ресерч и тестирование существующих решений 
+2 шаг - сбор релеваниного датасета и вывод нужной метрики
+3 шаг - выбор лучшего метода обработки, выбор архитектуры, тестирование на датасете
+4 шаг </t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Студент_587</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>@user_632</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>RL-bascket-recommendations</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Жду согласования</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Студент_930</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>@user_400</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>AI-навигация по строительному объекту на основе 360° контента</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1. Анализ научных статей 
+2. Формализация требований к конечному результату
+3. Исследование и анализ по собранным данным
+4. Разработка модуля сопоставления 3d кадров для создания трека с сопоставление</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Студент_345</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>@user_633</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Обучение с подкреплением для оптимизации недифферецируемых метрик в рекомендательных системах для ритейла</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Постановка задачи.
+У бизнеса есть потребность строить рекомендательные системы направленные на оптимизацию таких метрик как выручка, маржа, маржинальность и т.д. Зачастую данные метрики невозможно опт</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Студент_946</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>@user_416</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Голосовой тренажер для операторов поддержки</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Пока на стадии обсуждения и распредления ролей.</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Студент_656</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>@user_634</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Nastavnik</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Студент_320</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>@user_635</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>AI-ассистент по пользовательской документации КОМПАС-3D</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Жду ответ от руководителя. 
+Сегодня(13 октября) получили ответ от руководителя проекта такой: 
+« Да, сейчас готовим план работ, исходные данные и инфраструктуру. На этой неделе обязательно проведем и</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Студент_1495</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>@user_636</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Manuspect Virtual Assistant</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Студент_589</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>@user_637</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Высоконагруженная система транскрибации речи
+Кейсодатель: X5 Tech</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>План работы:
+1. Собрать скоуп по текущему проекту, составить подробный план со сравнением архитектур сервисов и архитектур моделей
+2. Протестировать качество и производительность различных конфигураци</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Студент_358</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>@user_227</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Газпромбанк (сегментация клиентов и рекомендация продуктов)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Добавили в чат проекта, жду план</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Студент_349</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>@user_364</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Genotek Biogotchi</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>На данном этапе мы обсудили концепт проекта, познакомились с командой, распределились по ролям. Конкретную дорожную карту проекта с четкими шагами мы должны определить на этой неделе, но лично я плани</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Студент_494</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>@user_081</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>HR-assistant</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Реализовать MVP сервиса автоматизированного поиска резюме на hh.ru
+1. Реализовать backend для сервиса 
+2. Реализовать механизм отправки запросов по апи с интеллектуальной фильтрацией
+3. Реализовать ме</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Студент_776</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>@user_288</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Улучшение навыков понимания text-rich изображений у VLM</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Хочется улучшать VLM понимать текст на изображении лучше. Отвечать на вопросы пользователей с учетом не только визуальной сцены на картине, но и того текста и его смысла, который она распознает. В это</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Студент_1505</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>@user_638</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Нет проекта</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Пока что нет плана так как нет проекта</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Студент_195</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>@user_639</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>AI навигация 360</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>В процессе обсуждения</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Студент_351</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>@user_138</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Customer Choice Models</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1. Онбординг
+2. Изучение различных статей по теме
+3. Эксперименты с изученными архитектурами/моделями из статей
+4. Определение наилучшей в поставленной задаче</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Студент_868</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>@user_344</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Автоматизация формирования сетевых планов благоустроительных работ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>План работы на текущий момент не составлен. В планах разработка MVP</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Студент_094</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>@user_089</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Turbo Sorter</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1) Сбор и анализ данных обращений: источники, объем, структура. Выявление типов и тем обращений, определение проблемных зон.
+2) Сбор информации из открытых источников и изучение релевантной литератур</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Студент_965</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>@user_435</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>AI-ассистент по пользовательской документации КОМПАС-3D</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В рамках проектной практики я бы хотел расширить свой опыт новыми технологиями и подходами, команда разносторонняя и сильная, будет возможность проконсультироваться.
+Дополню когда будет известен план </t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Студент_735</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>@user_258</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Автономная LLM-система верифицируемого знания</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Разработать веб-сервис на FastAPI, RAG систему (скорее всего), интеграцию с LLM</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Студент_841</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>@user_329</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Turbo Sorter</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1) Сбор и анализ данных обращений: источники, объем, структура. Выявление типов и тем обращений, определение проблемных зон.
+2) Сбор информации из открытых источников и изучение релевантной литератур</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Студент_621</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>@user_168</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Turbo Sorter</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1) Сбор и анализ данных обращений: источники, объем, структура. Выявление типов и тем обращений, определение проблемных зон.
+2) Сбор информации из открытых источников и изучение релевантной литератур</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Студент_1524</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>@user_357</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Доработка open-source инструментов по безопасности агентских систем</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Исследование OpenAI Agent Guardrails (как устроен, как работает, какие типы ошибок перехватывает, какие нет), сравнение с  open-source  инструментами.
+Доработка open-source инструментов по безопасност</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Студент_272</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>@user_309</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Turbo Sorter</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1) Сбор и анализ данных обращений: источники, объем, структура. Выявление типов и тем обращений, определение проблемных зон.
+2) Сбор информации из открытых источников и изучение релевантной литератур</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Студент_680</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>@user_209</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Джейн – AI-ассистент преподавателя урбанистики</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>- Структурировать предоставленные источники и оцифровать часть из них через OCR.
+- Настроить векторную базу данных с простой и удобной функцией добавления/обновления источников.
+- Расширить сценарии д</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Студент_682</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>@user_213</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>AI-компаньон для профориентации</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Доработать MVP с хакатона - повысить точность, устойчивость, и внедрить запланированные TODO</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Студент_942</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>@user_410</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>HR-assistant</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Реализовать MVP сервиса автоматизированного поиска резюме на hh.ru
+1. Реализовать backend для сервиса 
+2. Реализовать механизм отправки запросов по апи с интеллектуальной фильтрацией
+3. Реализовать ме</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Студент_899</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>@user_373</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Сервис поиска по структурированной информации</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Изучение решений на рынке, проектирование архитектуры системы по нотации С4, реализация минимальной версии проекта, тестирование</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Студент_221</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>@user_102</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Джейн AI-ассистент преподавателя урбанистики</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Структурирование предоставленных источников и оцифровка части из них через OCR.
+- Настроить векторную базу данных с простой и удобной функцией добавления/обновления источников.
+- Расширить сценарии </t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Студент_657</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>@user_193</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Матчинг адресов</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1)Изучение теоретических аспектов нормализации, разбора адресов на компоненты и алгоритмов информационного поиска/матчинга
+2)Проектирование пайплайна обработки адресов
+3) Выбор метрик для оценки каче</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Студент_149</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>@user_478</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>AI-ассистент КОМПАС-3D</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Проект такой: разработка инструмента, позволяющего упростить процесс обучения и использования ПО. Собрать в единую базу знаний многочисленные инструкции, справки, описания методик, вебинары и семинары</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Студент_484</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>@user_076</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>GigaStudio</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1) Улучшение инфраструктуры агентского AI;
+2) Реализация бизнес-фичей Gen AI в PDLC;
+3) Подготовка продукта к public beta.</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Студент_362</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>@user_482</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>praxis-core</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Установочная встреча с командой и руководителями для согласования требований, ожиданий, правил работы и дедлайнов.
+2. Итеративная работа двухнедельными спринтами.
+3. Релиз в конце каждого спринта, </t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Студент_951</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>@user_422</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Ранжирование каталога в мобильном приложении доставки еды</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Этап 1: Анализ данных и требований;
+Этап 2: Проектирование системы;
+Этап 3: Разработка модели;
+Этап 4: Инфраструктура и развертывание;
+Этап 5: Документирование и завершение</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Студент_515</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>@user_101</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Исследования SMMR для соц. сети Пульс с учетом временной компоненты</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Необходимо повысить разнообразие рекомендаций в ленте "Интересные посты" в соц. сети Пульс. В данный момент рекомендации на одну и ту же тему могут следовать подряд, чтобы бороться с этим и повысить р</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Студент_305</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>@user_111</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Автономная LLM-система верифицируемого знания</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Задача: построить RAG, который будет принимать ссылку на GitLab и использовать оттуда .md документы. Ответы должны быть релевантными и иметь референсы к материалу из документации.
+Моей же задачей буде</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Студент_444</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>@user_046</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Nettyan</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1. Backend разработка - миграция базы данных с SQLite на Postgres:
+Настройка миграции к БД и миграция существующей БД
+Внедрение ORM в коде Python для новой версии базы данных
+Развёртывание новой БД, в</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Студент_886</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>@user_640</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>antei</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>пока еще прохожу отбор в этот проект</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Студент_010</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>@user_641</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>AI ассистент для автоматизации работы в облаке</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Создание PoC новой версии агента, расширение его функционала</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Студент_213</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>@user_388</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>втономная LLM-система верифицируемого знания</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">На данный момент еще нет конкретного пошагового плана, он будет сформирован после 13 октября. Но уже сейчас можно выделить шаги, которые я собираюсь выполнить для достижения качественного результата:
+</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Студент_716</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>@user_243</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>AI Security Lab</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Тема - A2A2.
+Это новый стандарт для защиты многоагентных ИИ-систем, предложенный  видными специалистами в облсти AI-security.
+Сейчас стандарт только развивается, и мы хотим попробовать приложить к н</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Студент_511</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>@user_642</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Перезачёт</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Студент_1571</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>@user_643</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Помощник оператора call центра (OZON БАНК)</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Присоединился только на днях, жду онбординга и бэклога задач</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Студент_685</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>@user_644</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Цифровой генеалог</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>План работы
+1. Ознакомиться с требованиями заказчика
+2. Ознакомиться с алгоритмами онлайн-поиска в различных архивах
+3. Провести исследование на тему реализации мультиагентных систем
+4. Реализовать по</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Студент_822</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>@user_317</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>AI Media Producer</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Общая задача выглядит так: Инструмент для раскадровки, где сцена фиксируется как 3D-пространство, а кадры получаются движением камеры внутри этой сцены и затем стилизуются диффузионной моделью.
+В этом</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Студент_950</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>@user_421</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Цифровой генеалог</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1. Ознакомиться с требованиями заказчика
+2. Ознакомиться с алгоритмами онлайн-поиска в различных архивах
+3. Провести исследование на тему реализации мультиагентных систем
+4. Реализовать поиск человека</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Студент_1582</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>@user_044</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Система управления исследовательскими проектами (продуктовые и DS исследования)</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1. Выдвинуть гипотезы + прогнозы
+2. Проработать вопросы по шаблону проблемного интервью
+3. Показать руководителю, объединить с существующим шаблоном, согласовать план на интервью
+4. Провести проблемны</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Студент_365</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>@user_270</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Оптимизация логистических процессов в железнодорожных перевозках с помощью внедрения AI Агента</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1. Встретиться с командой, собрать ожидания от заказчика
+2. Описать бизнес-процесс, понять, что именно должен делать агент для заказчика, описать бизнес-требование
+3. Оформить метрики эффективности пи</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Студент_968</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>@user_439</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>praxis-core</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Установочная встреча с командой и руководителями для согласования требований, ожиданий, правил работы и дедлайнов.
+2. Итеративная работа двухнедельными спринтами.
+3. Релиз в конце каждого спринта, </t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Студент_625</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>@user_172</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>praxis-core</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Установочная встреча с командой и руководителями для согласования требований, ожиданий, правил работы и дедлайнов.
+2. Итеративная работа двухнедельными спринтами.
+3. Релиз в конце каждого спринта, </t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Студент_702</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>@user_232</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Record Linkage: ML-система сопоставления каталогов</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Анализ данных и формулировка гипотез:
+- получить и изучить датасеты
+- выявить потенциальные ключи для сопоставления
+- сформулировать и зафиксировать рабочие гипотезы
+- подготовить отчёт с выводами
+Со</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Студент_228</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>@user_247</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Цифровая бухгалтерия. Модуль цифровизации отдела по учету ТМЦ (товарно-материальных ценностей).</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1. Распознавание таблиц, включающее: детекцию (сделано), распознавание структуры, извлечение текста из ячеек  и формирование итогового файла с извлеченными структурированными данными
+2. Извлечение тек</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Студент_296</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>@user_645</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>MindEscape</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Основная задача — развитие игры Mind Escape и участие в смежных проектах компании Agnetics, включая управленческую и инженерную деятельность.
+Таким образом, план включает следующие этапы:
+    1. Финал</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Студент_743</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>@user_266</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Голосовой тренажер для операторов поддержки</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Примерный план по результатам встречи по проектам Ozon Fintech:
+План реализации:
+Этап 1: Проектирование системы сценариев и метрик (3 недели)
+Задача: cпроектировать детализированную схему сценариев</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Студент_821</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>@user_316</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>AI Media Producer</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Задача: разработка агентной системы для итеративной генерации изображений через цикл "генерация-критика-планирование" с использованием локальных или бюджетных облачных решений.
+Этапы выполнения:
+1. Ис</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Студент_736</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>@user_646</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Анализ end-to-end моделей диаризации</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Мотивация: качество диаризации существенно влияет на восприятие клонинга в видеопереводе, end-to-end модели вероятно позволят улучшить качество в сложных сценариях.
+План:
+1. Введение в предметную обл</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Студент_356</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>@user_024</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Создание ИИ-ассистента для организации</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Создать MVP проекта ассистента и его тестирование</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Студент_1610</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>@user_647</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>НАЁМ</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>План семестра заключается в проработке и уточнении архитектуры AI-платформы, включая возможный пересмотр структуры компонентов и способов взаимодействия между сервисами после утверждения конечного вид</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Студент_482</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>@user_648</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Скоринг модель для физ. лиц МТС Банка</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1. Определиться с местом развертки модели 
+2. Продумать необходимый объем данных (в БД банка есть много нюансов)
+3. Сформировать список сложностей перед реализацией прототипа (например, раз в месяц по</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Студент_1614</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>@user_086</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>AI-инструмент для предсказания и оптимизации свойств антител</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1. Обзор литературы
+2. Сформировать и очистить датасеты публичных последовательностей антител с терапевтически значимыми характеристикам (например, внутриклеточная стабильность для разработки intabodi</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Студент_118</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>@user_473</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>нет проекта :(</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1) найти проект</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Студент_1623</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>@user_649</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>A2AS</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Исследование и коммит в open source</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Студент_1624</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>@user_460</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>МРТ</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>еще обсуждаю с руководителем формат (научный или индустриальный)</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Студент_1626</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>@user_159</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Расширение экспертизы матрицы MITRE ATLAS</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Расширить экспертизу матрицы атак MITRE ATLAS для того, чтобы сделать ее применимой в задачах консалтинга в сфере AI Security. Для этого нужно: 1. Изучить имеющиеся вектора атак, связанные с ними инци</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Студент_158</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>@user_255</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>AI-агент для аварийного обслуживания оборудования</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1. настройка RAG
+2. обучение и тестирование ассистента
+3. работа с промптами.</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Студент_1629</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>@user_312</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>TensorTalks</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>TensorTalks
+ AI-Симулятор прохождения технического собеседования для ML специалистов (в начале ML - Дальше расширение)
+Подготовка к собеседованиям (Теория, алгоритмы)
+Симулятор будет работать как в ви</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Студент_459</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>@user_057</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>TensorTalks</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>TensorTalks
+ AI-Симулятор прохождения технического собеседования для ML специалистов (в начале ML - Дальше расширение)
+Подготовка к собеседованиям (Теория, алгоритмы)
+Симулятор будет работать как в ви</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Студент_840</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>@user_328</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Курс  для НИУ ВШЭ по машинному обучению</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>По методологии:
+- составить план и программу у дисциплины
+- написать план лекций
+- составить домашки
+- формализовать критерии для проекта
+из того что уже есть: https://drive.google.com/file/d/1kqshUnh</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Студент_196</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>@user_650</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ЖигулИИ Trainer</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>План работы на семестр
+Этап 1: Проектирование и архитектура
+Определение архитектуры системы и основных компонентов
+Проектирование формата конфигурационных файлов для описания проверок
+Разработка спец</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Студент_810</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>@expert_249</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ЖигулИИ Trainer</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Этап 1: Проектирование и архитектура
+Определение архитектуры системы и основных компонентов
+Проектирование формата конфигурационных файлов для описания проверок
+Разработка спецификации health-checks д</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Студент_803</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>@expert_083</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ЖигулИИ Trainer</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>План работы на семестр
+Этап 1: Проектирование и архитектура
+Определение архитектуры системы и основных компонентов
+Проектирование формата конфигурационных файлов для описания проверок
+Разработка спец</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Студент_581</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>@expert_127</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ЖигулИИ Trainer</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Этап 1: Проектирование и архитектура
+Определение архитектуры системы и основных компонентов
+Проектирование формата конфигурационных файлов для описания проверок
+Разработка спецификации health-checks д</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Студент_550</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>@user_119</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Построение траектории развития таланта в AI TH</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Установочная встреча будет 16 октября</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Студент_741</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>@user_264</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Построение траектории развития таланта в AI TH</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Обсуждение - 16 октября с командой и кейсодателями. 
+Краткий план (свой):
+- Сбор болей
+- Идеи по подходам
+- Создание roadmap
+- Реализация mvp части по рекомендации траектории
+- Доработки согласно фидб</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Студент_866</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>@expert_044</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Построение траектории развития таланта в AITH</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Установочная встреча 16 октября</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Студент_504</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>@expert_193</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Воркшоп по прототипированию игрового агента на основе LLM</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Основная задача - создать курс (дофиналить идею) и подготовить курс для ведения и апробации на площадке AITH.  
+Таким образом, план включает следующие этапы:
+1. Финализировать концепцию, идейную час</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Студент_378</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>@user_009</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Воркшоп по прототипированию игрового агента на основе LLM</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Основная задача \- разработать материалы и наполнение для курса, чтобы подготовить его к апробации на площадке AI Talent Hub.  
+Таким образом, план включает следующие этапы:
+1. Сформировать наполнени</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Студент_426</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>@user_033</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Разработка автономного тренажёра для обучения AI Security</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- разработать тестовый стенд LLM+RAG, на котором студенты могут отрабатывать навыки тестирования и защиты
+- получить доступ к разработке на базе Киберполигона ФБИТ ИТМО
+- спроектировать и разработать </t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Студент_749</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>@expert_238</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Образовательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Adapstory</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>На данный момент проводим глубокий рисерч и CustDev. Будем разрабатывать агентов для образования, построение курсов в телеграм</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Студент_748</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>@expert_239</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Fixly</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Ссылка на презентацию и питч: https://disk.yandex.ru/d/sWeHjB8vjDtlyw
+Лендинг: https://project15836736.tilda.ws/
+1. Привлечь 5-10 мастеров на бесплатное пилотное тестирование через лендинг.
+2. Обрабо</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Студент_259</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>@user_080</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Adapstory - персонализированное обучение</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Мы делаем:
+Создать веб-платформу и конструктор диалогов, которые через доставку контента, вопросы, RAG-поддержку и аналитический стек фиксируют не только результат (что сделал ученик), но и ход мыслей</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Студент_447</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>@user_651</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Memorix</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Продуктовые исследования и проектирование MVP версии продукта
+2. Доработка MVP на основе решенческих интервью и обратной связи
+3. Успешное окончание преакселератора ИТМО и поступление на программу </t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Студент_599</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>@user_153</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Adapstory</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1.Исследование рынка, ЦА и развитие идеи
+2.Пройти акселератор 
+3.Разработать MVP 
+4.Протестировать MVP на целевой аудитории</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Студент_1667</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>@user_652</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>LexFlow</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1. Пользователи и безопасность
+- Ввести регистрацию, подтверждение почты и вход (FastAPI Users / OAuth2 JWT / сторонний IdP). Мигрировать схему БД (добавить email, хеш пароля, статусы)
+- Реализовать у</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Студент_314</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>@user_491</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>PsyGhost</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Закончить дообучение ml модели, реализовать веб-интерфейс, закончить работу над мобильными приложением</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Студент_1670</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>@user_097</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Kuvio</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Сделать MVP, провести 10 продуктовых интервью</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Студент_180</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>@user_070</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>MODERA</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Продуктивизация кодовой базы;
+Исследование новых архитектур для обучения генеративных моделей для виртуальной примерочной;
+Стилист - подбор искусственным интеллектом похожих стилей на более качественн</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Студент_443</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>@user_045</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>НИТЬ</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Еще в процессе</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Студент_140</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>@user_397</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Пока что нет проекта</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Пока что нет проекта</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Студент_1680</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>@user_653</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Looqs</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Занимаюсь ML частью проекта Looqs, который мы уже презентовали в рамках AITH. Startup Track и демо дня 11.10.
+В течение семестра:
+- уже провели запуск pre-MVP в России на мужской аудитории
+Предстоит
+</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Студент_427</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>@user_035</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>приложение для подбора персональной программы питания</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Найти или собрать датасет
+Разработать рекомендательную систему и метрики качества
+Разработать серверную часть приложения</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Студент_847</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>@user_335</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Приложение для подбора персональной программы питания</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Поиск и парсинг данных для обучения модели и рекомендации 
+2. Выбор и имплементация архитектуры рекомендательной системы
+3. Разработка обертки - само приложение
+4. Тестирование </t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Студент_962</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>@user_433</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>PrediSense</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>У нас уже есть готовый продукт, который работает, в нем уже более 30 пользователей.
+Планы на этот семестр: развивать далее проект, работать с экспертами в рамках стартап акселератора, найти научника и</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Студент_174</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>@expert_242</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>SAYIT</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1) Создание pdf-агента
+Агент, который работает в качестве репетитора в realtime, используя pdf задачники
+2) Создание LLM-practice-card 
+LLM, которая на основе ошибок пользователей создает интерактивны</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Студент_839</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>@user_327</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ProductiveSocial</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. выполнить задачи на AITH Startup Track
+2.  Начинать разработкку микросервисов проекта </t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Студент_294</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>@user_654</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>AgentArea</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Зарелизить платформу. Сделать 10 продаж. Податься на бизнес-тезис и пройти.
+Провести 30 дополнительных кастдевов относительно дальнейших фичей.</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Студент_163</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>@expert_060</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>koteln(ai)a</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Cust-dev - ы для подтверждения гипотезы продукта.
+Окончание инкубатора Студент_2259 (отбор прошли, теперь инкубируемся).
+Определение основных технических параметров (и процессов системы в целом) кот</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Студент_1693</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>@user_655</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SAYIT</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Наш стартап представляет собой инновационное решение для практики иностранных языков – голосового ассистента, который помогает пользователям не только общаться на иностранном языке, но и совершенствов</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Студент_952</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>@user_415</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Стартап</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>OCR for egyptology</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>"нужно будет тюнить vlm, чтобы  они распознавали текст и может быть делали детекцию символов. 
+Сформулировать это как предложить новый способ использования модели, чтобы она хорошо решала нашу задачу.</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Студент_062</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>@expert_067</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Тренировка Vae Latent Upscalers для современных видеомоделей</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Название проекта пока рабочее, планирую написать классную статью и попробвать с ней податься на ICLR, CVPR и тому подобные конфы</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Студент_066</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>@user_170</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emoji Jailbreak </t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отвечать ревьюерам конференций, дорабатывать статью </t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Студент_036</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>@user_358</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Оптимизируемые мульти-агентные системы для эмоционального интеллекта ИИ</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Октябрь - Изучение базы
+Анализ существующих подходов к эмоциональному ИИ
+Обзор архитектур мульти-агентных систем
+Выбор датасетов и метрик оценки
+Ноябрь - Концептуальная работа
+Проектирование архитект</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Студент_914</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>@user_386</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Middle Egyptian Translator</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Хотим продолжать двигаться в синтезе данных для малоресурсных языков, применить новые и более продвинутые методы, возможно переложить их на другие языки</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Студент_028</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>@expert_202</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>LDARNet: DNA Adaptive Representation Network with Learnable Tokenization for Genomic Modeling</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>В течение семестра планирую реализовать полный цикл проекта по развитию архитектуры новой геномной Foundation Model. На первом этапе будет проведена разработка и экспериментальная проверка ключевых ар</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Студент_116</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>@expert_115</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Adaptive AutoML</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Обзор литературы: собрать существующие методы, метрики, сформулировать исследовательские вопросы
+2. Подготовка экспериментальной среды: выбрать несколько датасетов, несколько моделей, написать код </t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Студент_047</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>@user_359</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SwarmLM</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>1. Исследовать HLSMAC и LLM-PySC2 бенчмарки для тренировки и валидации моделей мульти-агентной системы
+2. Исследовать текущие архитектуры, используемые для решение задачи координации действий и коммун</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Студент_301</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>@user_481</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Explainability и механическая интерпретируемость для защиты LLM</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>На данный момент мы формируем план работ по исследованию методов RAG инъекций.
+План: разбор статей, блогпостов, отчетов об инцидентах; попытка воспроизведения атак, постановка экспериментов с новыми м</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Студент_009</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>@user_445</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Predictive maintenance</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Еще не успел подробно обсудить, но буду заниматься одной из 2 подтем: fault detection или эмбеддинги с информацией о состоянии автомобиля.
+Вероятно, план такой:
+1. Изучение датасетов, статей
+2. Воспро</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Студент_085</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>@user_381</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Модели глубокого обучения для обработки и интерпретации активности мозга</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>1) Финализация результатов foundation-моделей для ЭЭГ с предыдущих семестров, анализ результатов и интерпретируемости, написание статьи.
+2) Проектирование и обучение новой модели для совместного анали</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Студент_090</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>@user_237</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Модели глубокого обучения для обработки и интерпретации активности мозга</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>1) Финализация результатов foundation-моделей для ЭЭГ с предыдущих семестров, анализ результатов и интерпретируемости, написание статьи.
+2) Изучить статьи адаптирующие МЭГ для различных модальностей
+3</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Студент_957</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>@user_429</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Исследование мультиагентных систем в разных доменах</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>- Работа над треком MARL в рамках соревнования MindGames
+- Разработка МАС для автоматического написания статей (конкретные задачи будут определены позже)</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Студент_096</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>@user_060</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Health Index via Latent Cosine Similarity for Early-Stage Degradation</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Сейчас ребатлы на aaai, если не проходим отправляем статью в журнал.
+И начинаем новое исследование смежное с предыдущим.</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Студент_056</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>@expert_212</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>iMak AI Lab | Efficient Prompting</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Проверить ряд гипотез, основываясь на внутреннем представлении модели</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Студент_671</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>@user_203</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>NLP исследования</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Пока в процессе поиска темы исследования, ибо хотелось бы, чтобы практика в последствии стала ВКР</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Студент_011</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>@user_378</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Дубли в торговых новостях</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Пока нету</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Студент_740</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>@user_263</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Emotion-Driven Strategy in LLM Decision-Making</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Лит. обзор предметной области, поиск и внедрение новых игр для агентов в бенчмарк, разработка сильного манипулятивного агента (на основе больших опен-сорс моделей)</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Студент_959</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>@user_431</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Altyn AI</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>- Изучение текущего прогресса по проекту
+- Изучение SOTA подходов в text-to-sql системах
+- Повторяю SOTA на бенчмарке BIRD</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Студент_905</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>@user_377</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Бенчмарк для оценки влияния эмоциональных состояний на поведение LLM в сложных экономических и социальных задачах</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>1) Обзор литературы
+2) Проектирование и таксономия новых теоретико-игровых сценариев
+3) Сбор, синтетическая генерация и разметка датасетов под разные эмоциональные условия
+4) Проверка валидности сцена</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Студент_461</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>@user_061</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Бенчмарк для оценки влияния эмоций на поведение LLM моделей в контексте сложных экономических и социальных задач</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Анализ литературы и существующих подходов
+Разработка и классификация новых теоретико-игровых сценариев
+Сбор, генерация и разметка данных
+Валидация сценариев
+Интеграция в существующий бенчмарк и разраб</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Студент_474</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>@user_068</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Emotion-Driven Strategy in LLM Decision-Making</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1. Литобзор в области манипулятивных LLM-агентов и эмоциональным манипуляциям у людей/ у LLM
+2. Доработка текущего фреймворка, добавление новых игр в эксперименты
+3. Тестирование подходов к манипуляци</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Студент_661</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>@user_196</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Разработка  DNA LLM для решения задач геномики</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>амбициозный план
+1. исследование методов токенизации последовательностей ДНК
+2. обучение своего токенизатора
+3. обзор существующих архитектур DNA LLM, разработка своей собственной архитектуры
+4. пров</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Студент_958</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>@user_467</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Категоризатор e-commerce товаров</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Первая часть задачи - создание репрезентативного датасета.
+Была большая проблема с тем, что было непонятно, как и на чем тестировать решения по категоризации товаров. Требуется сделать такую разметку</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Студент_261</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>@user_656</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Агентская платформа</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Архитектурная проработка будущей системы, функциональная спецификация, дополнительно - прототипы универсальных агентских пайплайнов.</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Студент_328</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>@user_234</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Многофункциональная система на базе локальных моделей для автоматизации бизнес-процессов.</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Основной упор на повышение качества распознавания речи и улучшение качества генерации протоколов совещания.
+- подготовка пайплайна тестирования
+- эксперименты с опенсорс технологиями по предобработке,</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Студент_1725</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>@user_353</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Advancify</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Внедрить модели классификации учебной/неучебной активности, внедрить модель усталости глаз</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Студент_173</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>@user_657</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Lacmus Search</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Проект Lacmus Search представляет собой внутреннюю поисковую систему для консалтинговой компании. Система предназначена для поиска сотрудников по их навыкам и опыту и поддерживает два вида поиска: сво</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Студент_206</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>@user_297</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Цифровой двойник на базе ИИ для оптимизации заводнения нефтяных скважин</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>- Разработка моделей машинного обучения
+Создать ML-модели для прогнозирования поведения нефтедобычи, нефтеотдачи после заводнения и после введения агента в скважину.
+- Интеграция в платформу
+Внедрить</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Студент_829</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>@user_319</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>LP детектор</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. завести репозиторий
+2. собрать данных для детектора
+3. итеративно увеливаем  архитектуру детектора
+4. пробуем трансформерные детекторы </t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Студент_348</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>@expert_097</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Генеративный сервис для дизайнеров</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Основная задача на этот семестр вывести сервис на уровень рабочего прототипа, готового к комфортному тестированию. Планируется сосредоточиться на доработке и стабилизации основных функций, чтобы инстр</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Студент_781</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>@user_290</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>AI-ассистент для фермеров</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>1) Сбор требований заказчика к конечному продукту
+2) Выбор технологического стека
+3) Проработка архитектуры системы
+4) Продумывание сценариев работы системы
+5) Написание бейзлайнов агентов
+6) Интеграц</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Студент_344</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>@expert_169</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Исследование возможности использования генеративных моделей в задаче оценки состояния различных объектов на ПВЗ Wildberries</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Цель работы в семестре - Проанализировать и продемонстрировать на прототипах возможности диффузионных моделей для генерации интерьеров/входных групп ПВЗ Wildberries и детально исследовать объект «детс</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Студент_363</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>@user_272</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Memorix</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>1. Исследование и проектирование первой MVP версии продукта
+2. Разработка первой MVP версии продукта
+3. Доработка MVP и проведение тестирований с пользователями
+4. Деплой приложения в production</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Студент_780</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>@user_289</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Exam Builder: модульный MVP генерации и проверки тестов из материалов курса</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1. Парсеры: PDF/PPT → структурированный JSON со спанами и артефактами (таблицы/рисунки).
+2.Генератор двух треков вопросов: обычные (MCQ/истина-ложь/matching) и evidence-based (ответ со ссылкой на исто</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Студент_289</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>@user_414</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Индивидуальное ценообразование продуктов массового сегмента</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1. Аналитика клиентской базы
+2. Построение модели кластеризации клиентов по эластичности (много бизнес ограничений к модели)
+3. Построение модели индивидуальных условий вклада
+4. Построение интегральн</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Студент_292</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>@user_658</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Виртуальный ассистент</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>1) Провести исследование подходов к генерации липсинка на видео
+2) Провести анализ инструментов для извлечения аудио, поиска ответа по бд (RAG), генерации аудио ответа, объединения в единый ролик (рол</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Студент_354</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>@user_062</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Разработка модели бинарной классификации для удержания денежных средств клиентов банка</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Цель проекта:
+Разработать модель бинарной классификации, которая будет классифицировать клиентов (Юридические лица) с высоким риском вывода денежных средств из банка на основе их транзакционной активн</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Студент_236</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>@user_294</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>WideResearcher (Название может быть изменено)</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>1. Продумать идею до конца или до MVP решения
+2. Разработка микросервисной архитектуры
+3. Разработка дизайна веб-сервиса с продуманным userflow
+4. MVP разработка бэкэнда с заглушками под AI/ML-часть
+5</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Студент_315</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>@user_028</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Применение LLM для автоматизации бизнес-процессов ПАО Норильский Никель</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1. Анализ требований и архитектурное проектирование системы.
+2. Сбор, подготовка и структурирование данных.
+3. Разработка модуля проверки корректности и актуальности ЗНП.
+4. Реализация визуализации об</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Студент_816</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>@user_313</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Применение LLM для автоматизации бизнес-процессов ПАО Норильский Никель</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1. Анализ требований и архитектурное проектирование системы.
+2. Сбор, подготовка и структурирование данных.
+3. Разработка модуля проверки корректности и актуальности ЗНП.
+4. Реализация визуализации об</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Студент_895</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>@user_369</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Применение LLM для автоматизации бизнес-процессов ПАО Норильский Никель</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>1. Анализ требований и архитектурное проектирование системы.
+2. Сбор, подготовка и структурирование данных.
+3. Разработка модуля проверки корректности и актуальности ЗНП.
+4. Реализация визуализации об</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Студент_799</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>@user_301</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Джейн AI-ассистент преподавателя урбанистики</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1. Встреча с командой и обсуждение дальнейших работ по развитию продукта</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Студент_178</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>@user_659</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Пайплайн синтеза данных в 3D-среде для дообучения нейроредактора изображений пространственным операциям</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>3 семестр
+- собрать тестовый набор 3D-моделей, привести их к общему виду (возможно, алгоритмически)
+- написать пайплайн авто-генерации корректной произвольной 3D-сцены: выбор случайной среды, корректн</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Студент_280</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>@user_391</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Улучшение поиска в сервисе Циан</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>1. Разобраться в существующей системе текстового поиска объявлений
+2. Улучшить несколько частей: NER модель заполнения фильтров, transformer модель автодополнения текста, добавить LLM для перефраза
+3.</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Студент_786</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>@expert_156</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Гибридный поиск для чат-бота по продуктовой базе</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Определить метрики, сделать MVP, сравнить с прошлой иттерацией</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Студент_125</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>@user_464</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Развитие розничного моделирование в ПАО Газпромбанк</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>- Техническая реализация новой программы лояльности с помощью МЛ
+- Развитие и доработка децствующих моделей</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Студент_293</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>@user_660</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Нейростримерша NetTyan</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>- Сбор и классификация реальных (и при необходимости - синтетических) примеров токсичного, манипулятивного контента и джейлбрейк-запросов.
+-   Начало разработки и экспериментов по интеграции LLM-агент</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Студент_597</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>@user_151</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Разработка MVP-прототипа интеллектуальной игрушки AI-компаньона для детей 3–9 лет</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Октябрь — Этап исследований и проектирования
+Цель: провести исследование рынка и пользователей; определить требования, архитектуру и спецификации модулей системы.
+Основные задачи
+1. Исследование целе</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Студент_767</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>@user_278</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>copilot для врача</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рефактор архитектуры в рамках курса Архитектура микросервисов
+Реализация LocalAgreement для модели транскрибации 
+Тестирование новой модели онлайн диаризации
+Сбор метрик для транскрибации, диаризации </t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Студент_1002</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>@user_459</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Сервис интеллектуального поиска по строительной документации для  ООО «Студент_2256»</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Основные планы следующие
+1) Провести аудит текущих базы документов, имеющихся у компании ДжиминиСофт
+2) Провести детальную проработку арихтектуры решение и составление подробного ТЗ
+3) Провести экспе</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Студент_691</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>@user_661</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Text2SQL сервис для аналитики в X5</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>- внедрение функции поддержки нескольких таблиц и автоматический роутинг пользователя между ними
+- разработка механизма уточнений и рекомендации фильтров для пользователя</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Студент_683</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>@user_215</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>DealRocket.ru - лучший сервис поиска B2B клиентов в РФ</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1) Реализовать новый сервис для ранжирования выдачи информации на основе NLP модели
+2) Реализовать систему чат бота, который определяет фильтры для пользователя, так как сейчас есть проблема у пользов</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Студент_658</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>@user_194</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Анализ обратной связи клиентских менеджеров</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Основная задача - поиск инсайтов, указывающих на наличие ошибки в кампании продаж, в комментариях клиентских менеджеров к оферу для оперативной корректировки логики кампании
+План:
+- Анализ источников</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Студент_237</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>@user_007</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Adaptive Agents x AIRI</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Жду согласования проекта и дату</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Студент_814</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>@user_311</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>AI-компанибен для профориентации</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Разработка и тестирование AI-компаньона
+Парсинг данных профилей вузов, данных о актуальных курсах
+Обеспечение устойчивости генерации и проведения проф. ориентационных тестов
+Создание БД для пользовате</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Студент_638</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>@user_181</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>AI-компаньон для профориентации</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>1. Разработка и тестирование AI-компаньона
+2. Парсинг данных профилей вузов, данных о актуальных курсах
+3. Обеспечение устойчивости генерации и проведения проф. ориентационных тестов
+4. Создание БД дл</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Студент_454</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>@user_054</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Автоматизация формирования сетевых планов благоустроительных работ</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Цель:
+Сделать MVP системы, автоматически формирующей и сопровождающей сетевой план благоустроительных работ на основе проектных и ресурсных данных.
+Конкретные шаги сейчас на этапе обсуждения. Примерн</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Студент_622</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>@user_169</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Сервис кандидатогенерации на основе векторного поиска</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Улучшение RePlay валидационного пайплайна
+Добавление новых путей генерации кандидатов
+</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Студент_202</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>@user_182</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Гео-эмбеддинги: построение универсального представления локации</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1. Провести исследование моделей, способных формировать гео-эмбеддинги, выбрать несколько моделей для сравнительного анализа на прикладных задачах.
+2. Определить пул задач (бенчмарк) для сравнения кач</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Студент_312</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>@user_189</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Разработка агентной системы для генерации кода / для причинно-следственного анализа (точное направление в процессе согласования)</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>- Изучение релевантных научных статей и работ по агентным системам
+- Анализ возможных архитектур агентной системы, составление плана тестирования
+- Эксперименты с архитектурами и измерение метрик
+- Ан</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Студент_248</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>@expert_023</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>HiveTrace - мониторинг  LLM-приложений</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>в этом семестре основное внимание планируется уделить улучшению качества метрик цензурирования, повышению точности алгоритмов классификации нарушений, а также улучшению работы модуля обнаружения и очи</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Студент_1004</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>@user_463</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Бенчмарк DeepFake методов для борьбы с мошенниками</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Познакомиться с командой.
+2. Обсудить с командой и руководителем проект.
+3. Составить план. 
+4. Выполнить план. </t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Студент_242</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>@user_176</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Turbo Sorter</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>1) Сбор и анализ данных обращений: источники, объем, структура. Выявление типов и тем обращений, определение проблемных зон.
+2) Сбор информации из открытых источников и изучение релевантной литературы</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Студент_760</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>@user_274</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Страновые рейтинги</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-Найти научного руководителя
+-Собираюсь собрать актуальный набор данных
+-Пройти на нём все этапы, что я сделал на работе, а именно:
+1) Подготовка данных
+2) Обучение моделей
+3) Валидация результата
+</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Студент_184</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>@user_423</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Платформа автоматизированного таможенного декларирования на основе ИИ</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Разобраться с предметной областью таможенного декларирования
+2. Войти в курс дела: что уже сделано, что предстоит улучшить
+3. Подобрать подходы к использованию данных из PostgreSQL к использованию </t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Студент_298</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>@user_230</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Анализ сезонности товаров</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>1. Собрать данные по товарам
+2. Проанализировать данные
+3. Провести эксперимент с извлечением признаков сезонности с использованием подходов анализа временных рядов
+4. Провести эксперимент с использов</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Студент_308</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>@user_662</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>LLAMATOR: фреймворк для тестирования безопасности LLM-систем</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Реализовать MCP-сервер для фреймворка LLAMATOR, что позволит с лёгкостью интегрировать решение в агентные сети</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Студент_600</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>@user_155</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Biogotchi x Genotek</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>1. Изучение научных работ
+2. Поиск датасетов
+3. Постановка гипотез, проверка
+4. Разработка baseline решения, написание inference для интеграции в ЛК Genotek
+5. Разработка улучшений на основе данных/ар</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Студент_872</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>@user_348</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Цель: Разработка прототипа сервиса Sample для разделения музыки на инструменты.
+Задачи:
+1. Исследование и анализ: Изучение методов преобразования аудио в нотные партитуры и классических алгоритмов с</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Студент_136</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>@user_121</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>МРТ</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Сформировать представления о работе с МРТ снимками 
+Научиться работать с пайпланом fastMRI для восстановления МРТ снимков.
+Научиться работать с пайпланом fastMRI для детекции патологий.
+Определить эта</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Студент_721</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>@user_249</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Мониторинг и атаки в агентных системах</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Есть несколько направлений у AI Security Lab ( стартап HiveTrace), сейчас идет набор
+Так как проекты немного исследовательские - результат предугадать сложно</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Студент_270</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>@expert_029</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>LLAMATOR — Python-фреймворк для автоматического тестирования безопасности LLM-систем.</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Разработать MCP-сервер для фреймворка llamator, автоматизирующий процессы red teaming для LLM.</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Студент_746</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>@user_268</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Turbo Sorter</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>1) Сбор и анализ данных обращений: источники, объем, структура. Выявление типов и тем обращений, определение проблемных зон.
+2) Сбор информации из открытых источников и изучение релевантной литератур</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Студент_912</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>@user_663</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Разработка LLM-агента для ответов на вопросы по карточкам мест</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1. Провести анализ типовых запросов, создать инструменты агента, в частности тулы для поиска, анализа отзывов и инструменты работы с ресурсами.
+2. Оптимизировать взаимодействие между туллингом и LLM,</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Студент_1831</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>@expert_205</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Разработка и исследование методов тензорного параллелизма для оптимизации потребления памяти GPU в распределенном обучении больших языковых моделей.</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Доделать инженерную часть</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Студент_332</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>@user_664</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Помощник оператора call центра</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Изучить и протестировать инструменты для реального времени транскрибации речи (например, Whisper, Google Speech-to-Text).
+Разработать прототип системы RAG (Retrieval-Augmented Generation) для подсказ</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Студент_670</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>@user_443</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Сервис аналитики геоданных</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>1. Обзор данных для предсказаний и добавление новых источников
+2.Выделение 2-3 задач предсказания 
+3. Обучение модели и добавление прогнозов на карту</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Студент_856</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>@user_665</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Expired product detector</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Онбординг и подготовка:
+Согласование метрик (реальная точность/recall).
+Запуск окружения (Spark/ML-нод).
+EDA и воспроизведение baseline:
+Получение доступов к данным (приходы, продажи, списания), теку</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Студент_1837</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>@user_666</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>AI Sale Ассист</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>- Проведение продуктовых исследований и валидация продукта
+- Проведение технических исследований под первоначальную идею
+- Разработка базового MVP</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Студент_572</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>@user_204</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>АСКОН-ИТМО: AI-ассистент КОМПАС-3D</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>1. Сбор и подготовка данных для обучения: пасринг сайта справки, текстовых обучающих материалов, вебинаров и лекций.
+2. Формирование датасета для обучения, теста и валидации.
+3. Разработка архитектуры</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Студент_737</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>@user_261</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>AI Sale Ассист</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>- Проведение продуктовых исследований и валидация продукта
+- Проведение технических исследований под первоначальную идею
+- Разработка базового MVP</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Студент_1847</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>@expert_201</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>HiveTrace</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>В этом семестре основное внимание планируется уделить улучшению качества метрик цензурирования, повышению точности алгоритмов классификации нарушений, а также улучшению работы модуля обнаружения и очи</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Студент_764</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>@user_277</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>RL-Recomendations-Basket</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>планирую улучшииь модель рекомендации товаров для приложений x5 и исследовать возможность увеличения не деференцируемых метрик с помощью увеличения NDCG</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Студент_978</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>@user_470</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Сервис геоаналитики на открытых данных</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>1. Исследование публичных данных для задачи пространственного прогнозирования торговых и сервисных точек.
+2. Формулировка гипотез и генерация признаков.
+3. Формирование пайплайна с AutoML.</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Студент_706</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>@user_236</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Бенчмарк DeepFake методов для борьбы с мошенниками</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Обсуждение этапов работы над проектом и дальнейшее их осуществление на текущей итеррации только нашел</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Студент_243</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>@user_667</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Не знаю</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Трудно сказать</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Студент_652</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>@user_190</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Студент_1858</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>@user_668</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Автоматизация создания сетевых планов</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>1. Знакомство с отраслью и существующими решениями с похожим функционалом 2. Сбор и обработка данных 3. Создание архитектуры приложения 4. Обучение моделей</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Студент_582</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>@user_134</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Разработка инструментария по борьбе с фродом в сервисе авторизации</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Студент_1860</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>@user_669</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>HR-matcher</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/i/1uP0IHmcJWUx1A</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Студент_205</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>@user_670</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Применение LLM для автоматизации бизнес-процессов ПАО Норильский Никель</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>1. Анализ требований и архитектурное проектирование системы.
+2. Сбор, подготовка и структурирование данных.
+3. Разработка модуля проверки корректности и актуальности ЗНП.
+4. Реализация визуализации об</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Студент_608</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>@expert_096</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Платформа рантайм инференса векторных моделей</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>1. Подготовить TDR платформы
+2. Согласовать TDR со смежными командами, свести список early-adopter'ов
+3. Реализовать POC платформы</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Студент_233</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>@user_458</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Студент_1868</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>@user_671</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>MediaTracking</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>- подготовка данных и обучение базовой модели для определения тематики текстов
+- итеративное улучшение качества модели классификации, проведение экспериментов, оценка метрик и снижение количества "шум</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Студент_854</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>@expert_051</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>MLизация игровых механик</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>1)  Погружение в данные, механику продукта, основными метриками
+2) Аналитика/построение моделей 
+3) A/B тестирование
+4) Расчет LTV</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Студент_966</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>@user_437</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>MindEscape</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Совмещение 3д составляющий движка Unity и LLM модели в одном проекте
+Разработка MVP 3D игры с использованием пользовательского железа для реализации общения с LLM
+Разработка и реализация возможных мех</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Студент_279</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>@user_251</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Сервис по оценке качества работы экспертов фонда</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Общие положения
+1.1. Наименование работ
+Разработка системы анализа и оценки качества работы экспертов по оценке (экспертизе) конкурсных заявок НКО на финансирование с применением методов машинного </t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Студент_1875</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>@user_486</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Трекинг медиа-трендов</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>- Проектирование и реализация сервиса интересов пользователей
+- Связывание бэкенда приложения с мастер-данными, содержащими информацию о постах и разметки ML моделей
+- Создание простого клиентского пр</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Студент_862</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>@user_340</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Сервис по оценке качества работы экспертов фонда</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>План работы на семестр:
+1. Общие положения
+1.1. Наименование работ
+Разработка системы анализа и оценки качества работы экспертов по оценке (экспертизе) конкурсных заявок НКО на финансирование с приме</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Студент_953</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>@user_425</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>HR-assistant</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Реализовать MVP сервиса автоматизированного поиска резюме на hh.ru
+1. Реализовать backend для сервиса 
+2. Реализовать механизм отправки запросов по апи с интеллектуальной фильтрацией
+3. Реализовать ме</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Студент_787</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>@expert_177</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>VLMHyperBench - open-source фреймворк для оценки возможностей Vision Language Models (VLM) в распознавании русскоязычных документов.</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>1. Студент_2264 проекта полностью в сторону модульности и универсальности.
+2. Доработать инструменты деплоя релизов и протестировать их работу.
+3. Добавить поддержку задачи оценки VLM для задачи распо</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Студент_211</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>@user_430</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Нейростримерша NetTyan</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Проработка системы настроения и эмоций.
+- Реализовать подстановку соответствующих промптов в зависимости от текущего настроения персонажа.
+2. Геймификация и система достижений.
+- Описать иконки и </t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Студент_449</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>@user_049</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>MLизация игровых механик</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>1. Изучить структуру игровых логов (игровые сессии, время, действия, реклама, награды и т.д.).
+2. Определить ключевые метрики успеха: LTV, playtime, просмотры рекламы, retention и т.д.
+3. Провести EDA</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Студент_695</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>@expert_172</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Нейростримерша NetTyan</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Изучение основ
+Ознакомление с архитектурой Browser-Use и аналогичных систем (например, WebArena, AgentScope, ByteDance UI TARS).
+Изучение инструментов автоматизации браузера (Playwright, Puppeteer).
+П</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Студент_585</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>@user_137</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Нейростримерша NetYyan</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>- Изучить актуальные инструменты для взаимодействия по протоколу MCP на Python
+(клиент) и Java (сервер)
+- Разработать прототип MCP-клиента и MCP-сервера для управления персонажем в
+Minecraft
+- Внедрит</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Студент_808</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>@user_672</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Quick insight</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>1. Доделать ML пайплайн до состояния MVP - донастройка основных ML компонентов, написание ML сервисов
+2. Провести с командой сессию генерации гипотез для улучшений, сформировать бэклог, осуществить ко</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Студент_226</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>@user_259</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>HiveTrace - мониторинг  LLM-приложений</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>в этом семестре предусматривается развитие пользовательской платформы: улучшение интерфейса, расширение возможностей управления пользователями и политиками цензурирования, добавление визуализации метр</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Студент_907</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>@user_673</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>MediaTracking</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>- Перенести сбор данных на оркестратор данных - Dagster
+- Добавить Dag для обновления данных
+- Переработать БД и внедрить её в наши сервис
+- Подготовить сервис для параллельного сбора данных с ТГ кана</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Студент_903</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>@expert_200</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>(примерно) Применение нейросетевых моделей для оценки кредитного риска</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Октябрь: работа с данными (транзакции, история БКИ), нужные согласования, сбор выборок для моделирования, генерация признаков, исследование подходов
+Ноябрь-Декабрь: моделирование, проверка гипотез на </t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Студент_239</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>@user_157</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Индустриальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Использование генерации синтетических данных для улучшения качества RAG</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>1. Обзор материалов.
+Прочитать статьи  для рассмотрения существующих подходов и выбора метрик и датасетов
+2. Реализация гипотез по улучшения качества ретрива и проведение экспериментов по замеру соотв</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Студент_896</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>@user_370</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Научный</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Пока не определено</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Студент_804</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>@user_305</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Valde</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Планирую продолжить работу по устранению ошибок, работать с  оптимизацией кодовой базы. Подобрать датасет с мероприятиями. Синтезировать данные, если не удаётся подобрать датасет с мероприятиями. Так </t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Студент_325</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>@user_440</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/import_ready/projects.xlsx
+++ b/data/import_ready/projects.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -508,11 +508,7 @@
           <t>@user_582</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Образовательный</t>
@@ -542,11 +538,7 @@
           <t>@user_154</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Образовательный</t>
@@ -578,11 +570,7 @@
           <t>@user_583</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Образовательный</t>
@@ -613,7 +601,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>EdTech, NLP, Agents</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -648,11 +636,7 @@
           <t>@user_341</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Образовательный</t>
@@ -680,11 +664,7 @@
           <t>@user_058</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -707,11 +687,7 @@
           <t>@user_336</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -734,11 +710,7 @@
           <t>@user_042</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -766,11 +738,7 @@
           <t>@user_152</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,7 +767,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>CV, Recsys</t>
         </is>
       </c>
     </row>
@@ -827,11 +795,7 @@
           <t>@user_584</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -858,7 +822,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>NLP, Agents, ASR</t>
         </is>
       </c>
     </row>
@@ -885,11 +849,7 @@
           <t>@user_586</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -916,7 +876,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>Recsys</t>
         </is>
       </c>
     </row>
@@ -943,7 +903,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>TimeSeries, RL, Industrial</t>
         </is>
       </c>
     </row>
@@ -972,11 +932,7 @@
           <t>@user_587</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1000,11 +956,7 @@
           <t>@user_320</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1031,11 +983,7 @@
           <t>@user_208</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1062,7 +1010,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>CV, NLP, Industrial</t>
         </is>
       </c>
     </row>
@@ -1089,11 +1037,7 @@
           <t>@user_590</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1118,11 +1062,7 @@
           <t>@user_356</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1151,7 +1091,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>Agents</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1120,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>Recsys, NLP, Agents, AgriTech</t>
         </is>
       </c>
     </row>
@@ -1206,11 +1146,7 @@
           <t>@user_591</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1237,7 +1173,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>CV</t>
         </is>
       </c>
     </row>
@@ -1267,11 +1203,7 @@
           <t>@user_310</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1297,7 +1229,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>NLP, Agents, ASR, TTS</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1256,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>CV, NLP, Agents</t>
         </is>
       </c>
     </row>
@@ -1349,11 +1281,7 @@
           <t>@user_072</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1379,11 +1307,7 @@
           <t>@user_593</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1409,11 +1333,7 @@
           <t>@user_116</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1436,11 +1356,7 @@
           <t>@user_594</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1463,11 +1379,7 @@
           <t>@user_597</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1497,7 +1409,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>NLP</t>
         </is>
       </c>
     </row>
@@ -1524,11 +1436,7 @@
           <t>@user_598</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1551,11 +1459,7 @@
           <t>@user_300</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1579,11 +1483,7 @@
           <t>@user_161</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1611,7 +1511,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>MedTech</t>
         </is>
       </c>
     </row>
@@ -1637,11 +1537,7 @@
           <t>@user_343</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1667,11 +1563,7 @@
           <t>@user_392</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1696,11 +1588,7 @@
           <t>@user_218</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1724,11 +1612,7 @@
           <t>@user_184</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1751,11 +1635,7 @@
           <t>@user_043</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1779,11 +1659,7 @@
           <t>@user_601</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1807,11 +1683,7 @@
           <t>@user_222</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1834,11 +1706,7 @@
           <t>@user_412</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1861,11 +1729,7 @@
           <t>@user_142</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1888,11 +1752,7 @@
           <t>@user_602</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1917,11 +1777,7 @@
           <t>@user_411</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1946,11 +1802,7 @@
           <t>@user_306</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1975,11 +1827,7 @@
           <t>@user_603</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2006,11 +1854,7 @@
           <t>@user_200</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2039,7 +1883,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Научный</t>
+          <t>CV</t>
         </is>
       </c>
     </row>
@@ -2064,11 +1908,7 @@
           <t>@user_229</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2091,11 +1931,7 @@
           <t>@user_050</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2121,11 +1957,7 @@
           <t>@user_604</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2148,11 +1980,7 @@
           <t>@user_165</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2178,11 +2006,7 @@
           <t>@user_221</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2205,11 +2029,7 @@
           <t>@user_114</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2233,11 +2053,7 @@
           <t>@user_304</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2262,11 +2078,7 @@
           <t>@user_064</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2292,11 +2104,7 @@
           <t>@user_125</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2322,11 +2130,7 @@
           <t>@user_003</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2349,11 +2153,7 @@
           <t>@user_375</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2378,11 +2178,7 @@
           <t>@user_295</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2405,11 +2201,7 @@
           <t>@user_318</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2433,11 +2225,7 @@
           <t>@user_605</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2460,11 +2248,7 @@
           <t>@user_606</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2490,11 +2274,7 @@
           <t>@user_607</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2517,11 +2297,7 @@
           <t>@user_608</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2546,11 +2322,7 @@
           <t>@user_273</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2575,11 +2347,7 @@
           <t>@user_447</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2604,11 +2372,7 @@
           <t>@user_201</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2634,11 +2398,7 @@
           <t>@user_420</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2661,11 +2421,7 @@
           <t>@user_395</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2691,11 +2447,7 @@
           <t>@user_260</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2718,11 +2470,7 @@
           <t>@user_180</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2745,11 +2493,7 @@
           <t>@user_609</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2775,11 +2519,7 @@
           <t>@user_610</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2803,11 +2543,7 @@
           <t>@user_352</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2832,11 +2568,7 @@
           <t>@user_004</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2861,11 +2593,7 @@
           <t>@user_020</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2891,11 +2619,7 @@
           <t>@user_053</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2920,11 +2644,7 @@
           <t>@user_612</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2948,11 +2668,7 @@
           <t>@user_013</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2975,11 +2691,7 @@
           <t>@user_178</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3002,11 +2714,7 @@
           <t>@user_030</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3031,11 +2739,7 @@
           <t>@user_614</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3059,11 +2763,7 @@
           <t>@user_245</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3087,11 +2787,7 @@
           <t>@user_027</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3116,11 +2812,7 @@
           <t>@user_206</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3146,11 +2838,7 @@
           <t>@user_073</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3175,11 +2863,7 @@
           <t>@user_402</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3205,11 +2889,7 @@
           <t>@user_214</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3232,11 +2912,7 @@
           <t>@user_302</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3261,11 +2937,7 @@
           <t>@user_405</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3288,11 +2960,7 @@
           <t>@user_239</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3318,11 +2986,7 @@
           <t>@user_453</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3348,11 +3012,7 @@
           <t>@user_092</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3378,11 +3038,7 @@
           <t>@user_616</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3408,11 +3064,7 @@
           <t>@user_282</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3435,11 +3087,7 @@
           <t>@user_006</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3465,11 +3113,7 @@
           <t>@user_279</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3494,11 +3138,7 @@
           <t>@user_291</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3524,11 +3164,7 @@
           <t>@user_205</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3552,11 +3188,7 @@
           <t>@user_617</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3580,11 +3212,7 @@
           <t>@user_298</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3610,11 +3238,7 @@
           <t>@user_434</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3641,11 +3265,7 @@
           <t>@user_014</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3668,11 +3288,7 @@
           <t>@user_618</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3695,11 +3311,7 @@
           <t>@user_619</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3723,11 +3335,7 @@
           <t>@user_380</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3750,11 +3358,7 @@
           <t>@user_002</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3777,11 +3381,7 @@
           <t>@user_620</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3806,11 +3406,7 @@
           <t>@user_436</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3834,11 +3430,7 @@
           <t>@user_621</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3861,11 +3453,7 @@
           <t>@user_059</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3889,11 +3477,7 @@
           <t>@user_241</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3922,7 +3506,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>CV</t>
         </is>
       </c>
     </row>
@@ -3949,11 +3533,7 @@
           <t>@user_622</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3978,11 +3558,7 @@
           <t>@user_067</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4008,11 +3584,7 @@
           <t>@user_079</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4035,11 +3607,7 @@
           <t>@user_408</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4065,7 +3633,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>NLP</t>
         </is>
       </c>
     </row>
@@ -4092,11 +3660,7 @@
           <t>@user_314</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4120,11 +3684,7 @@
           <t>@user_140</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4148,11 +3708,7 @@
           <t>@user_624</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4175,11 +3731,7 @@
           <t>@user_071</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4202,11 +3754,7 @@
           <t>@user_262</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4229,11 +3777,7 @@
           <t>@user_136</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4260,11 +3804,7 @@
           <t>@user_625</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4289,7 +3829,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>CV, NLP, ASR, TTS</t>
         </is>
       </c>
     </row>
@@ -4314,11 +3854,7 @@
           <t>@user_090</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4341,11 +3877,7 @@
           <t>@user_626</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4369,11 +3901,7 @@
           <t>@user_627</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4396,11 +3924,7 @@
           <t>@user_226</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4427,7 +3951,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Agents, NLP</t>
         </is>
       </c>
     </row>
@@ -4457,11 +3981,7 @@
           <t>@user_363</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4487,11 +4007,7 @@
           <t>@user_406</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4518,11 +4034,7 @@
           <t>@user_452</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4547,11 +4059,7 @@
           <t>@user_628</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4576,11 +4084,7 @@
           <t>@user_238</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4606,11 +4110,7 @@
           <t>@user_127</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4635,11 +4135,7 @@
           <t>@user_085</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4662,11 +4158,7 @@
           <t>@user_629</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4694,7 +4186,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>CV, NLP</t>
         </is>
       </c>
     </row>
@@ -4721,11 +4213,7 @@
           <t>@user_487</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4750,11 +4238,7 @@
           <t>@user_631</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4780,11 +4264,7 @@
           <t>@user_632</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4807,11 +4287,7 @@
           <t>@user_400</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4837,11 +4313,7 @@
           <t>@user_633</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4865,11 +4337,7 @@
           <t>@user_416</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4894,7 +4362,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>NLP, ML</t>
         </is>
       </c>
     </row>
@@ -4921,11 +4389,7 @@
           <t>@user_636</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4951,11 +4415,7 @@
           <t>@user_227</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4978,11 +4438,7 @@
           <t>@user_364</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5005,11 +4461,7 @@
           <t>@user_081</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5035,11 +4487,7 @@
           <t>@user_288</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5062,11 +4510,7 @@
           <t>@user_638</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5089,11 +4533,7 @@
           <t>@user_138</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5121,7 +4561,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Recsys</t>
         </is>
       </c>
     </row>
@@ -5146,11 +4586,7 @@
           <t>@user_089</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5174,11 +4610,7 @@
           <t>@user_435</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5203,7 +4635,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Agents, NLP</t>
         </is>
       </c>
     </row>
@@ -5229,11 +4661,7 @@
           <t>@user_309</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5258,11 +4686,7 @@
           <t>@user_213</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5287,7 +4711,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Agents, EdTech, Recsys, NLP</t>
         </is>
       </c>
     </row>
@@ -5314,7 +4738,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>NLP</t>
         </is>
       </c>
     </row>
@@ -5341,11 +4765,7 @@
           <t>@user_193</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5372,7 +4792,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>NLP, ML</t>
         </is>
       </c>
     </row>
@@ -5397,11 +4817,7 @@
           <t>@user_076</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5426,11 +4842,7 @@
           <t>@user_482</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5455,11 +4867,7 @@
           <t>@user_422</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5484,7 +4892,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Recsys</t>
         </is>
       </c>
     </row>
@@ -5512,11 +4920,7 @@
           <t>@user_640</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5539,11 +4943,7 @@
           <t>@user_641</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5566,11 +4966,7 @@
           <t>@user_388</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5594,11 +4990,7 @@
           <t>@user_243</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5621,11 +5013,7 @@
           <t>@user_644</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5652,11 +5040,7 @@
           <t>@user_317</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5682,11 +5066,7 @@
           <t>@user_270</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5711,11 +5091,7 @@
           <t>@user_439</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5745,7 +5121,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Industrial, NLP</t>
         </is>
       </c>
     </row>
@@ -5771,11 +5147,7 @@
           <t>@user_645</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5800,11 +5172,7 @@
           <t>@user_266</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5829,11 +5197,7 @@
           <t>@user_024</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5856,11 +5220,7 @@
           <t>@user_647</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5885,11 +5245,7 @@
           <t>@user_086</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5913,11 +5269,7 @@
           <t>@user_473</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5940,11 +5292,7 @@
           <t>@user_649</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5969,7 +5317,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Другое</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -5994,11 +5342,7 @@
           <t>@user_255</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
+      <c r="E194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6023,11 +5367,7 @@
           <t>@user_312</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
+      <c r="E195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6055,7 +5395,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>EdTech, NLP</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -6090,11 +5430,7 @@
           <t>@user_650</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>Образовательный</t>
@@ -6126,11 +5462,7 @@
           <t>@expert_249</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>Образовательный</t>
@@ -6158,11 +5490,7 @@
           <t>@user_264</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>Образовательный</t>
@@ -6190,11 +5518,7 @@
           <t>@expert_193</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>Образовательный</t>
@@ -6225,11 +5549,7 @@
           <t>@user_009</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>Образовательный</t>
@@ -6259,7 +5579,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>EdTech</t>
         </is>
       </c>
     </row>
@@ -6289,7 +5609,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>NLP, Agents</t>
         </is>
       </c>
     </row>
@@ -6315,11 +5635,7 @@
           <t>@user_651</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6346,7 +5662,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>NLP, EdTech</t>
         </is>
       </c>
     </row>
@@ -6375,7 +5691,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>EdTech, NLP</t>
         </is>
       </c>
     </row>
@@ -6402,7 +5718,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Стартап</t>
+          <t>NLP, RL</t>
         </is>
       </c>
     </row>
@@ -6427,11 +5743,7 @@
           <t>@user_070</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6456,11 +5768,7 @@
           <t>@user_045</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6483,11 +5791,7 @@
           <t>@user_653</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6514,11 +5818,7 @@
           <t>@user_035</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6543,11 +5843,7 @@
           <t>@user_335</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6571,11 +5867,7 @@
           <t>@user_654</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>Стартап</t>
-        </is>
-      </c>
+      <c r="E213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6599,11 +5891,7 @@
           <t>@expert_067</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6626,11 +5914,7 @@
           <t>@user_170</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6653,11 +5937,7 @@
           <t>@user_358</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6685,11 +5965,7 @@
           <t>@user_386</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6712,11 +5988,7 @@
           <t>@expert_202</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6739,11 +6011,7 @@
           <t>@expert_115</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6767,11 +6035,7 @@
           <t>@user_359</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6795,11 +6059,7 @@
           <t>@user_481</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6825,11 +6085,7 @@
           <t>@user_381</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6853,11 +6109,7 @@
           <t>@user_237</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6881,11 +6133,7 @@
           <t>@user_060</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6909,11 +6157,7 @@
           <t>@expert_212</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6936,11 +6180,7 @@
           <t>@user_203</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6963,11 +6203,7 @@
           <t>@user_378</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6990,11 +6226,7 @@
           <t>@user_431</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7019,11 +6251,7 @@
           <t>@user_377</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7050,11 +6278,7 @@
           <t>@user_467</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7078,11 +6302,7 @@
           <t>@user_656</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7107,7 +6327,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>NLP</t>
         </is>
       </c>
     </row>
@@ -7134,11 +6354,7 @@
           <t>@user_353</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7161,11 +6377,7 @@
           <t>@user_657</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7190,7 +6402,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>NLP</t>
         </is>
       </c>
     </row>
@@ -7218,11 +6430,7 @@
           <t>@user_319</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7248,11 +6456,7 @@
           <t>@expert_097</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7277,7 +6481,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>CV</t>
         </is>
       </c>
     </row>
@@ -7307,11 +6511,7 @@
           <t>@expert_169</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7334,11 +6534,7 @@
           <t>@user_272</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7362,11 +6558,7 @@
           <t>@user_414</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7392,11 +6584,7 @@
           <t>@user_658</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7420,11 +6608,7 @@
           <t>@user_062</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7450,7 +6634,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>FinTech</t>
         </is>
       </c>
     </row>
@@ -7479,11 +6663,7 @@
           <t>@user_028</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7511,7 +6691,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Industrial, RAG, NLP, Agents</t>
         </is>
       </c>
     </row>
@@ -7538,11 +6718,7 @@
           <t>@user_391</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7567,11 +6743,7 @@
           <t>@expert_156</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7594,11 +6766,7 @@
           <t>@user_464</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7622,11 +6790,7 @@
           <t>@user_660</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7652,7 +6816,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Agents, NLP</t>
         </is>
       </c>
     </row>
@@ -7680,11 +6844,7 @@
           <t>@user_278</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7710,11 +6870,7 @@
           <t>@user_459</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -7738,11 +6894,7 @@
           <t>@user_215</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7766,11 +6918,7 @@
           <t>@user_194</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7795,11 +6943,7 @@
           <t>@user_007</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7822,11 +6966,7 @@
           <t>@user_311</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -7852,11 +6992,7 @@
           <t>@user_181</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7883,7 +7019,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Recsys</t>
         </is>
       </c>
     </row>
@@ -7909,11 +7045,7 @@
           <t>@user_189</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -7939,11 +7071,7 @@
           <t>@expert_023</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7966,11 +7094,7 @@
           <t>@user_463</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7998,7 +7122,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>FinTech</t>
         </is>
       </c>
     </row>
@@ -8031,7 +7155,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>FinTech</t>
         </is>
       </c>
     </row>
@@ -8058,11 +7182,7 @@
           <t>@user_230</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8088,11 +7208,7 @@
           <t>@user_662</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8115,11 +7231,7 @@
           <t>@user_155</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8146,11 +7258,7 @@
           <t>@user_348</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8175,11 +7283,7 @@
           <t>@user_121</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8203,11 +7307,7 @@
           <t>@expert_029</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8230,11 +7330,7 @@
           <t>@user_268</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8258,11 +7354,7 @@
           <t>@expert_205</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8285,11 +7377,7 @@
           <t>@user_664</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8313,11 +7401,7 @@
           <t>@user_443</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8342,11 +7426,7 @@
           <t>@user_665</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8373,11 +7453,7 @@
           <t>@user_666</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8402,11 +7478,7 @@
           <t>@user_204</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8431,11 +7503,7 @@
           <t>@user_261</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8458,11 +7526,7 @@
           <t>@user_277</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8485,11 +7549,7 @@
           <t>@user_470</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8514,11 +7574,7 @@
           <t>@user_236</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8541,11 +7597,7 @@
           <t>@user_190</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8568,11 +7620,7 @@
           <t>@user_134</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8597,7 +7645,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>NLP</t>
         </is>
       </c>
     </row>
@@ -8626,7 +7674,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Recsys, Industrial</t>
         </is>
       </c>
     </row>
@@ -8654,7 +7702,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Индустриальный</t>
+          <t>Backend, NLP</t>
         </is>
       </c>
     </row>
@@ -8682,11 +7730,7 @@
           <t>@user_437</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -8711,11 +7755,7 @@
           <t>@user_486</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -8740,11 +7780,7 @@
           <t>@user_340</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -8769,11 +7805,7 @@
           <t>@user_430</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -8800,11 +7832,7 @@
           <t>@user_672</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -8828,11 +7856,7 @@
           <t>@user_259</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -8856,11 +7880,7 @@
           <t>@user_157</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>Индустриальный</t>
-        </is>
-      </c>
+      <c r="E293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -8885,11 +7905,7 @@
           <t>@user_370</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>Научный</t>
-        </is>
-      </c>
+      <c r="E294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -8914,7 +7930,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Другое</t>
+          <t>Recsys, NLP</t>
         </is>
       </c>
     </row>

--- a/data/import_ready/projects.xlsx
+++ b/data/import_ready/projects.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Тематики</t>
+          <t>Теги</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
